--- a/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
@@ -575,46 +575,46 @@
         <v>66</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.554044380815348</v>
+        <v>-8.5266228288504</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.471589724355681</v>
+        <v>3.460616661317978</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.56151089290384</v>
+        <v>1.556405324457891</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.340356088204388</v>
+        <v>-1.335885772378589</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.153618265085321</v>
+        <v>1.150170253262715</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06520731251995215</v>
+        <v>-0.06506412153768082</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.667634361650038</v>
+        <v>-1.662007766299347</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.171522949245613</v>
+        <v>-5.154810430283028</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.874791501380408</v>
+        <v>3.862756430885042</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.01326143214047448</v>
+        <v>-0.01294579075021574</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.819454880571975</v>
+        <v>2.810422369079141</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.854630793170664</v>
+        <v>2.845482526514104</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9141298533135824</v>
+        <v>0.9112633237859669</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3553096483141971</v>
+        <v>-0.3539463568185468</v>
       </c>
     </row>
     <row r="7">
@@ -624,49 +624,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.876154369593252</v>
+        <v>-1.894749965468911</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.723493026787168</v>
+        <v>-4.768116531941409</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.526619377313423</v>
+        <v>3.560328260536266</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.461761689922774</v>
+        <v>-7.532763478617134</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.530994683813269</v>
+        <v>-5.583757548452866</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.234484625577721</v>
+        <v>-5.283642078814495</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.793749769041284</v>
+        <v>-7.868234625776061</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.026994214098877</v>
+        <v>-7.094187522511398</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.378666079014081</v>
+        <v>-3.411254419228406</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.955296525631809</v>
+        <v>1.972915752942448</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.20896643830519</v>
+        <v>1.220645952723508</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.243312151094656</v>
+        <v>1.255328084193962</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.8278057948059825</v>
+        <v>0.835516796529653</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.638969681186545</v>
+        <v>-2.664552417424602</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.595479136536504</v>
+        <v>-7.736098105090718</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.044085956063938</v>
+        <v>-1.065019158145645</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.904653770056271</v>
+        <v>-1.93706664157137</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.793705295824736</v>
+        <v>-2.848587774459467</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.285836451243071</v>
+        <v>-1.312504234461663</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.056768425957692</v>
+        <v>-4.132122855730977</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.07499636033468</v>
+        <v>-1.099441812863709</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.670668155712512</v>
+        <v>-7.814652016946972</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.644977232430222</v>
+        <v>-3.713974387270056</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.467456039681196</v>
+        <v>-3.53138836333958</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.463794186453356</v>
+        <v>2.509606930952387</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5698415771225598</v>
+        <v>-0.5791606915900331</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.032759988009104</v>
+        <v>-3.087787994353498</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8637761772797958</v>
+        <v>0.8771142492425383</v>
       </c>
     </row>
     <row r="9">
@@ -728,49 +728,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.914490951789162</v>
+        <v>-0.924747825629062</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.790696582256963</v>
+        <v>3.820735759762179</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.554514184943045</v>
+        <v>6.609024740236471</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.313244696699037</v>
+        <v>8.379105503027702</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.675125702611204</v>
+        <v>5.719983932355518</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.024345135143221</v>
+        <v>7.080505290546249</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.835782063051433</v>
+        <v>4.873037928737325</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.69963556431016</v>
+        <v>10.78390367769445</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.585787108030424</v>
+        <v>9.662563542872512</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.635403306290009</v>
+        <v>6.688816232757475</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.321009977595651</v>
+        <v>4.357509186141478</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.302042560309843</v>
+        <v>3.329549710537933</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2784310081695907</v>
+        <v>-0.2812950262971157</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.140718631618924</v>
+        <v>-2.159233268487945</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>134</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.730442276805121</v>
+        <v>2.724572306022644</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3726906512972761</v>
+        <v>0.3718748537431793</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.02220739423500362</v>
+        <v>-0.02275914137285184</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1079870605023103</v>
+        <v>0.1079634141966181</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.17739878234854</v>
+        <v>-1.17427873572008</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.133121094606409</v>
+        <v>-0.1327423434509711</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.770192844767529</v>
+        <v>2.763787591127922</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8084794552477561</v>
+        <v>0.8069420714855084</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.485373008885162</v>
+        <v>4.47426662139361</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.634910489421529</v>
+        <v>3.625824444417468</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4393102944849048</v>
+        <v>0.4376457057353207</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.02210864910063</v>
+        <v>-1.019892278321343</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0520778611151087</v>
+        <v>0.05214416074687023</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.546572130411874</v>
+        <v>2.540671463172075</v>
       </c>
     </row>
     <row r="11">
@@ -832,49 +832,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.62926106629309</v>
+        <v>7.70554696291039</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.019415986258409</v>
+        <v>6.081546545661837</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.32879679337038</v>
+        <v>1.345207943420441</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3820360548168296</v>
+        <v>-0.3870182305999137</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9206306797566839</v>
+        <v>0.9288716390742664</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.465524575606821</v>
+        <v>-2.491369040726241</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.134081943044087</v>
+        <v>1.144879424160827</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.581489198663306</v>
+        <v>5.637682623664752</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.064262386449421</v>
+        <v>3.097675926868817</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.170845422106652</v>
+        <v>3.205429084889168</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.96657944664571</v>
+        <v>3.000021594886711</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.617153538453593</v>
+        <v>3.655682058685613</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.236618830121145</v>
+        <v>7.310881529802359</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.795350328950633</v>
+        <v>3.83389478754448</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>211</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3607368984090229</v>
+        <v>-0.3601080370838048</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8716361765920126</v>
+        <v>0.8692226309777382</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.002590408248821063</v>
+        <v>0.001880749835130757</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6068252497975379</v>
+        <v>0.6057791738209843</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.06824179420576826</v>
+        <v>0.06828659803560555</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8402738211308787</v>
+        <v>0.8387719972032173</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.704805277765701</v>
+        <v>1.701232627994607</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.085023456069131</v>
+        <v>-2.08072786984458</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7025095348479411</v>
+        <v>0.7003363784428487</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.048402978435391</v>
+        <v>-2.044681281891883</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1206770088850249</v>
+        <v>0.1195394627040827</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.269866033200643</v>
+        <v>-1.267715821220555</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.216100667082834</v>
+        <v>-1.214036782876462</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.44114788009896</v>
+        <v>-1.43824909988917</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2946657690093559</v>
+        <v>0.2952554343187401</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.5734974594892819</v>
+        <v>-0.5739270635072202</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5189974670016255</v>
+        <v>0.5204837441032737</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6491475144346879</v>
+        <v>0.6501068262795044</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.749430560429857</v>
+        <v>-1.752582427695003</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.524657438219023</v>
+        <v>1.527103035538545</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.04848069453311155</v>
+        <v>-0.04845557118664345</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8889887164284858</v>
+        <v>-0.8905813441459927</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9495904303732559</v>
+        <v>-0.9505783813529973</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.429267078214757</v>
+        <v>-1.431361487125095</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.633958352177778</v>
+        <v>-1.63599989480327</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.391242100722828</v>
+        <v>-1.393272870099274</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.438262909030207</v>
+        <v>-1.440393152685886</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3013378468464367</v>
+        <v>0.3018654930231577</v>
       </c>
     </row>
     <row r="14">
@@ -988,49 +988,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.142444942726534</v>
+        <v>-5.149793697931209</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.431428484907293</v>
+        <v>-5.43887804582576</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.507651870727663</v>
+        <v>-3.512124605868443</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.058778425399474</v>
+        <v>-1.060371708321753</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.08975284097607528</v>
+        <v>-0.0902551925543591</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4566886730527173</v>
+        <v>-0.4573058011027342</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.779009210503325</v>
+        <v>1.781685543324343</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.298293764283869</v>
+        <v>4.304353237529604</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.07438002630543394</v>
+        <v>-0.07402212562634958</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2594588775854305</v>
+        <v>-0.2596954834116687</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.118215219108727</v>
+        <v>-3.122256116699418</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7613299384119401</v>
+        <v>-0.7622915640051602</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.473002623860296</v>
+        <v>1.475261134020045</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.390687585938444</v>
+        <v>1.392756552675067</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>324</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.493438320209911</v>
+        <v>-2.487113365544005</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.180552603387113</v>
+        <v>-3.173219622693217</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4877079123329082</v>
+        <v>-0.4868431544604022</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.592593943771497</v>
+        <v>-1.588872871841886</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5874353974448354</v>
+        <v>-0.5855637497931809</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6368331521859787</v>
+        <v>0.6355172610386646</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3744831718265118</v>
+        <v>-0.3742659645676198</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.460711996239247</v>
+        <v>-1.458347247027504</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.522308727791</v>
+        <v>-1.519820083052139</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.756219604151909</v>
+        <v>-1.752661317462923</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.961528573898491</v>
+        <v>-1.957414641780431</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.854959507964494</v>
+        <v>-2.848957410360924</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.584908831611635</v>
+        <v>-3.577853996614465</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.262684079073033</v>
+        <v>-4.254058590264108</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9156525888808105</v>
+        <v>0.9156665049181214</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.292984594963926</v>
+        <v>1.293443326404642</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.228252270573471</v>
+        <v>-2.230124476587477</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.235077662774771</v>
+        <v>-3.238167826880478</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.21568056156346</v>
+        <v>-1.217066792876246</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.487020552908369</v>
+        <v>-1.488224874128264</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.132953769210012</v>
+        <v>-4.136244805476565</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.452921046030994</v>
+        <v>-2.4548410339236</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.04693246467721934</v>
+        <v>0.0471314838993564</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.65615850143049</v>
+        <v>-1.657694555829359</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7220252853672733</v>
+        <v>-0.7228467405457906</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4029114769552393</v>
+        <v>-0.4035632983001491</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8850014351844919</v>
+        <v>0.8855838001566596</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2806750698044027</v>
+        <v>0.2806042777320314</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>321</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7800426815806176</v>
+        <v>-0.7760630142338769</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.328561693458802</v>
+        <v>-3.319097854812817</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.541509332337384</v>
+        <v>-1.536988331541309</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.264090087248661</v>
+        <v>3.258814725176904</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.102127460058398</v>
+        <v>2.098805908453116</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.277074372441909</v>
+        <v>-2.271242000335988</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.115523385663195</v>
+        <v>-1.11187351765647</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9589877832109863</v>
+        <v>-0.9562259708471359</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7075269417048489</v>
+        <v>-0.7063898303696945</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.624537654627531</v>
+        <v>0.6241703428578305</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.141911084621476</v>
+        <v>-1.138215380213637</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.419914553438922</v>
+        <v>-1.415358702618924</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2788303232771483</v>
+        <v>-0.2779809148099304</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.215102226491759</v>
+        <v>-2.208944940789017</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>298</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.1911254381792844</v>
+        <v>0.1940804058928265</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.116434220441768</v>
+        <v>-5.097590708955337</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.839463536464464</v>
+        <v>-4.82341382888449</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.037413857743879</v>
+        <v>-4.023986576226861</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.561216634773054</v>
+        <v>-2.552571830260341</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9215947096665857</v>
+        <v>-0.9170685238026124</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.025578557941586</v>
+        <v>-3.014791351084547</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-5.847233610309885</v>
+        <v>-5.829141916791265</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.565152528257791</v>
+        <v>-4.552382847158555</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.746325004070805</v>
+        <v>-4.73136709258921</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.615913749343974</v>
+        <v>-4.600549947108128</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.918415732135045</v>
+        <v>-4.901737259561315</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-5.001269034615831</v>
+        <v>-4.986421400707599</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.724054899950382</v>
+        <v>-1.716565840243391</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.583814898674149</v>
+        <v>1.584066268484463</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.791667924879</v>
+        <v>2.791617404141178</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.965447070192035</v>
+        <v>1.965521798783378</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.806288612958781</v>
+        <v>0.8049077127911133</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.272159243380223</v>
+        <v>3.275884095280659</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.71104194712747</v>
+        <v>2.713975227516585</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4797427440227864</v>
+        <v>0.4779773356161954</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4443410193092276</v>
+        <v>0.4420814654872984</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8109642596034305</v>
+        <v>0.8109589718646859</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.03646206358459381</v>
+        <v>-0.03916621316315627</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6202497178538593</v>
+        <v>0.6181494280365172</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.945910467297026</v>
+        <v>1.945636033657756</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.487202516337803</v>
+        <v>-1.491859956597445</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.66790704809415</v>
+        <v>-1.673173107079776</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.777918463709625</v>
+        <v>1.779013896202287</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.848730526139057</v>
+        <v>-2.86545062279167</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.238574107107503</v>
+        <v>-2.250802160915661</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.108320974500003</v>
+        <v>-2.119783251729601</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.154279878014442</v>
+        <v>-4.16839607775831</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.569163662578831</v>
+        <v>-1.575661077282888</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.372789719545224</v>
+        <v>2.374688271263459</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.411756700545155</v>
+        <v>2.412844894822662</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.851285162443894</v>
+        <v>2.857284294052221</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5110619958083049</v>
+        <v>-0.5180934162282824</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2925948498742059</v>
+        <v>0.2872542695551417</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.837679468355276</v>
+        <v>1.836788942052088</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.417680029925684</v>
+        <v>1.416534331107187</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1566999010662684</v>
+        <v>0.1511041482319584</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.792839517814727</v>
+        <v>-2.842795769043839</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.410401154731112</v>
+        <v>-1.476105063429635</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.002874651746872</v>
+        <v>-3.072941087176801</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7201928521180818</v>
+        <v>0.6974833924083015</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.81224033900196</v>
+        <v>-2.866163905481542</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.11958882044798</v>
+        <v>-0.1343256485528315</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4660632073244528</v>
+        <v>-0.4910332786170244</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8681819832561928</v>
+        <v>0.8548828715501671</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.264076469428375</v>
+        <v>-1.284129847361967</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3149379676636315</v>
+        <v>0.2899873918525202</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.682452537695902</v>
+        <v>-1.732947750646879</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.053036989727708</v>
+        <v>-1.092503987240868</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.8732325372674765</v>
+        <v>-0.9066979921251601</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5778635900148572</v>
+        <v>0.5551445522723668</v>
       </c>
     </row>
     <row r="22">
@@ -2213,10 +2213,8 @@
           <t>X &gt; 0.5058</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.0428165206488913</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; 0.5497</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4022~4035</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4022</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.09640058933153028</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; 0.5937</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3942~3954</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3942</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.136809530068227</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; 0.6376</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3846~3856</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3846</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.3333251652672047</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; 0.6816</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3752~3761</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3752</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.3648440514996807</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; 0.7255</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3618~3627</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3618</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.2774467087395678</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; 0.7695</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3457~3464</t>
-        </is>
+      <c r="B12" t="n">
+        <v>3457</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.06849605693052752</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; 0.8135</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3246~3253</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3246</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.04954037984723669</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; 0.8574</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2978~2984</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2978</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.08056968750219795</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.9014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2677~2682</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2677</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.4894103002225378</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.9453</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2353~2358</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2353</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.89926736257204</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.9893</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2002~2006</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2002</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.8963921882646062</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 1.033</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1681~1685</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1681</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.215760492846407</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 1.077</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1383~1387</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1383</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.435905587504514</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 1.121</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1151~1154</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1151</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.406041749114117</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 1.165</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>953~955</t>
-        </is>
+      <c r="B21" t="n">
+        <v>953</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.328551208585836</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 1.209</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>788~788</t>
-        </is>
+      <c r="B22" t="n">
+        <v>788</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.201993151871235</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 1.253</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>651~651</t>
-        </is>
+      <c r="B23" t="n">
+        <v>651</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.423612371034267</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 1.297</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>538~538</t>
-        </is>
+      <c r="B24" t="n">
+        <v>538</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.4805393749573099</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 1.341</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>450~450</t>
-        </is>
+      <c r="B25" t="n">
+        <v>450</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.1732283464566891</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 1.385</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>355~355</t>
-        </is>
+      <c r="B26" t="n">
+        <v>355</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.43613914457876</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 1.429</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>302~302</t>
-        </is>
+      <c r="B27" t="n">
+        <v>302</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.48007161356486</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 1.473</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>257~257</t>
-        </is>
+      <c r="B28" t="n">
+        <v>257</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.203059734264734</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 1.517</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>227~227</t>
-        </is>
+      <c r="B29" t="n">
+        <v>227</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>2.132112340582978</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 1.561</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>189~189</t>
-        </is>
+      <c r="B30" t="n">
+        <v>189</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.9457151189434683</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 1.605</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>157~157</t>
-        </is>
+      <c r="B31" t="n">
+        <v>157</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>4.194459768961998</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 1.649</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>133~133</t>
-        </is>
+      <c r="B32" t="n">
+        <v>133</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.641900025654685</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 1.693</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B33" t="n">
+        <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.09276857634174718</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 1.736</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>100~100</t>
-        </is>
+      <c r="B34" t="n">
+        <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.5065616797900248</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 1.78</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B35" t="n">
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>3.458942632170981</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; 0.5058</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.077990251218594</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; 0.5497</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>150~150</t>
-        </is>
+      <c r="B7" t="n">
+        <v>150</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-3.16010498687664</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; 0.5937</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>230~231</t>
-        </is>
+      <c r="B8" t="n">
+        <v>230</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-2.709888536660188</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; 0.6376</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>326~329</t>
-        </is>
+      <c r="B9" t="n">
+        <v>326</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-4.165170843006329</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; 0.6816</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>420~424</t>
-        </is>
+      <c r="B10" t="n">
+        <v>420</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-3.436834546625072</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; 0.7255</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>554~558</t>
-        </is>
+      <c r="B11" t="n">
+        <v>554</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.955803911607823</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; 0.7695</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>715~721</t>
-        </is>
+      <c r="B12" t="n">
+        <v>715</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.2111386562116593</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; 0.8135</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>926~932</t>
-        </is>
+      <c r="B13" t="n">
+        <v>926</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.08166897592735722</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; 0.8574</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1194~1201</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1194</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.1293760011888594</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.9014</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1495~1503</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1495</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.9298987327182928</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.9453</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1819~1827</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1819</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-1.207176689120764</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.9893</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2170~2179</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2170</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.8642506194297965</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 1.033</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2491~2500</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2491</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.8534383202099747</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 1.077</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2789~2798</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2789</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.7421874267146293</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 1.121</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3021~3031</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3021</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.563382233110012</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 1.165</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3219~3230</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3219</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.4191349146372261</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 1.209</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3384~3397</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3384</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.5358286646315236</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 1.253</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3521~3534</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3521</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.2863075901590406</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 1.297</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3634~3647</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3634</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.09420607452859286</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 1.341</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3722~3735</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3722</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.04363912342282816</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 1.385</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3817~3830</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3817</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2480075108105027</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 1.429</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3870~3883</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3870</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.1370128759658371</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 1.473</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3915~3928</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3915</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.1003629637945025</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 1.517</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3945~3958</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3945</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.1437667689214379</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 1.561</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3983~3996</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3983</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.06601089278254335</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 1.605</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>4015~4028</t>
-        </is>
+      <c r="B31" t="n">
+        <v>4015</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.1846001871414487</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 1.649</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>4039~4052</t>
-        </is>
+      <c r="B32" t="n">
+        <v>4039</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.07487958378352033</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 1.693</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>4056~4069</t>
-        </is>
+      <c r="B33" t="n">
+        <v>4056</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.02354399728050538</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 1.736</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>4072~4085</t>
-        </is>
+      <c r="B34" t="n">
+        <v>4072</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.03321800197252855</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 1.78</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B35" t="n">
+        <v>4088</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.09158511367498789</v>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>66</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.5266228288504</v>
+        <v>-8.514148519182612</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.460616661317978</v>
+        <v>3.473489697452543</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.556405324457891</v>
+        <v>1.569377295513114</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.335885772378589</v>
+        <v>-1.322940400115769</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.150170253262715</v>
+        <v>1.163251696331315</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.06506412153768082</v>
+        <v>-0.05204769085494831</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.662007766299347</v>
+        <v>-1.648965491605956</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.154810430283028</v>
+        <v>-5.14165140183006</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.862756430885042</v>
+        <v>3.875939532873282</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.01294579075021574</v>
+        <v>0.0004456841916962162</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.810422369079141</v>
+        <v>2.823869929292307</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.845482526514104</v>
+        <v>2.858928331644925</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9112633237859669</v>
+        <v>0.9248159805224745</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3539463568185468</v>
+        <v>-0.3643759925166989</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>80</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.894749965468911</v>
+        <v>-1.882106360548299</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.768116531941409</v>
+        <v>-4.755080228683767</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.560328260536266</v>
+        <v>3.573471859836481</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.532763478617134</v>
+        <v>-7.519651121752084</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.583757548452866</v>
+        <v>-5.570507167960223</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.283642078814495</v>
+        <v>-5.270456564917993</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.868234625776061</v>
+        <v>-7.855022381735964</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.094187522511398</v>
+        <v>-7.08085495880426</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.411254419228406</v>
+        <v>-3.397899048418275</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.972915752942448</v>
+        <v>1.986484832588111</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.220645952723508</v>
+        <v>0.5318388304522017</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.255328084193962</v>
+        <v>1.268773458082698</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.835516796529653</v>
+        <v>0.8490693249875818</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.664552417424602</v>
+        <v>-2.674982053122754</v>
       </c>
     </row>
     <row r="8">
@@ -676,49 +676,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.736098105090718</v>
+        <v>-7.640292817354045</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.065019158145645</v>
+        <v>-1.039620661905246</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-1.93706664157137</v>
+        <v>-2.46452604459153</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.848587774459467</v>
+        <v>-2.803174352821657</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.312504234461663</v>
+        <v>-1.283646556997752</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.132122855730977</v>
+        <v>-4.074527543317501</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.099441812863709</v>
+        <v>-1.071935901155115</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.814652016946972</v>
+        <v>-7.716311328080984</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.713974387270056</v>
+        <v>-3.659972663147151</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.53138836333958</v>
+        <v>-3.480172790410833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.509606930952387</v>
+        <v>2.496621523081032</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5791606915900331</v>
+        <v>-0.5602027037199875</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.087787994353498</v>
+        <v>-3.041681418020936</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.8771142492425383</v>
+        <v>1.306976709763838</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>94</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.924747825629062</v>
+        <v>-0.9117822086301928</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.820735759762179</v>
+        <v>3.832781535404997</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.609024740236471</v>
+        <v>6.622031871654073</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>8.379105503027702</v>
+        <v>7.811841699756847</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.719983932355518</v>
+        <v>5.731600964096963</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.080505290546249</v>
+        <v>7.091689188206374</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.873037928737325</v>
+        <v>4.884865400559335</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.78390367769445</v>
+        <v>10.79431432752681</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.662563542872512</v>
+        <v>9.673239714086066</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.688816232757475</v>
+        <v>6.70046496662453</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.357509186141478</v>
+        <v>4.370966479851695</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.329549710537933</v>
+        <v>3.342095461548979</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2812950262971157</v>
+        <v>-0.2676493068882664</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.159233268487945</v>
+        <v>-2.169662904186097</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>134</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.724572306022644</v>
+        <v>2.736405446289304</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3718748537431793</v>
+        <v>0.3846585183036737</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.02275914137285184</v>
+        <v>-0.009752009955249719</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1079634141966181</v>
+        <v>0.1209425565950824</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.17427873572008</v>
+        <v>-1.160854290159975</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1327423434509711</v>
+        <v>-0.1196855089794298</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.763787591127922</v>
+        <v>2.77611914902397</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8069420714855084</v>
+        <v>0.8199321636730588</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.47426662139361</v>
+        <v>4.486216440171262</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.625824444417468</v>
+        <v>3.638208481792716</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4376457057353207</v>
+        <v>0.4511029994455384</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.019892278321343</v>
+        <v>-1.006202120848165</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.05214416074687023</v>
+        <v>0.0657033939074978</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.540671463172075</v>
+        <v>2.530241827473922</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>161</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.70554696291039</v>
+        <v>7.716072189764944</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.081546545661837</v>
+        <v>6.092864765994591</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.345207943420441</v>
+        <v>1.358215074838043</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3870182305999137</v>
+        <v>-0.3740390882014495</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.9288716390742664</v>
+        <v>0.941912645674627</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.491369040726241</v>
+        <v>-2.477434054652541</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.144879424160827</v>
+        <v>1.157812017400509</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.637682623664752</v>
+        <v>5.649458530788635</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.097675926868817</v>
+        <v>3.110114030197359</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>3.205429084889168</v>
+        <v>2.871844899347167</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.000021594886711</v>
+        <v>3.013478888596929</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.655682058685613</v>
+        <v>3.668141269988048</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.310881529802359</v>
+        <v>6.972087402209965</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.83389478754448</v>
+        <v>3.823465151846328</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>211</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3601080370838048</v>
+        <v>-0.3475333278780255</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.8692226309777382</v>
+        <v>0.881754935159563</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.001880749835130757</v>
+        <v>0.01488788125273288</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6057791738209843</v>
+        <v>0.6187583162194485</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.06828659803560555</v>
+        <v>0.08137448976677319</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8387719972032173</v>
+        <v>0.8515763532707652</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.701232627994607</v>
+        <v>1.713769665816301</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.08072786984458</v>
+        <v>-2.066948469377692</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7003363784428487</v>
+        <v>0.7132150815973901</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.044681281891883</v>
+        <v>-2.031276154239052</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1195394627040827</v>
+        <v>0.1329967564143004</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.267715821220555</v>
+        <v>-1.253961439067403</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.214036782876462</v>
+        <v>-1.20048073652486</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.43824909988917</v>
+        <v>-1.448678735587322</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>268</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2952554343187401</v>
+        <v>0.3076844158844025</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.5739270635072202</v>
+        <v>-0.5609047474460169</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5204837441032737</v>
+        <v>0.5334908755208758</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6501068262795044</v>
+        <v>0.6630859686779687</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.752582427695003</v>
+        <v>-1.73881913855621</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.527103035538545</v>
+        <v>1.539706515978267</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.04845557118664345</v>
+        <v>-0.0353485015407955</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8905813441459927</v>
+        <v>-0.8770358788679928</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9505783813529973</v>
+        <v>-0.9371283998885218</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.431361487125095</v>
+        <v>-1.417956359472264</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.63599989480327</v>
+        <v>-1.622542601093052</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.393272870099274</v>
+        <v>-1.588853948574666</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.440393152685886</v>
+        <v>-1.426837106334283</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3018654930231577</v>
+        <v>0.2914358573250055</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>301</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.149793697931209</v>
+        <v>-5.135363084159714</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.43887804582576</v>
+        <v>-5.424026040833141</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.512124605868443</v>
+        <v>-3.499117474450841</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.060371708321753</v>
+        <v>-1.047392565923289</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.0902551925543591</v>
+        <v>-0.2601073607748887</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4573058011027342</v>
+        <v>-0.4441314284620788</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.781685543324343</v>
+        <v>1.794042419775842</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.304353237529604</v>
+        <v>4.315960161923847</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.07402212562634958</v>
+        <v>-0.0609224577455052</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2596954834116687</v>
+        <v>-0.2462903557588376</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.122256116699418</v>
+        <v>-3.108798822989201</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7622915640051602</v>
+        <v>-0.7488392752850501</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.475261134020045</v>
+        <v>1.488817180371647</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.392756552675067</v>
+        <v>1.382326916976915</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>324</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.487113365544005</v>
+        <v>-2.473379529458484</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.173219622693217</v>
+        <v>-3.158889322817643</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4868431544604022</v>
+        <v>-0.4738360230428</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.588872871841886</v>
+        <v>-1.575893729443422</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5855637497931809</v>
+        <v>-0.5724529454182417</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6355172610386646</v>
+        <v>0.6482628469393035</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.3742659645676198</v>
+        <v>-0.36118218219395</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.458347247027504</v>
+        <v>-1.444711066827942</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.519820083052139</v>
+        <v>-1.506132531341166</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.752661317462923</v>
+        <v>-1.739256189810092</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.957414641780431</v>
+        <v>-1.943957348070214</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.848957410360924</v>
+        <v>-2.835505121640814</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.577853996614465</v>
+        <v>-3.564297950262862</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.254058590264108</v>
+        <v>-4.264488225962261</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>351</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9156665049181214</v>
+        <v>0.9281885595258998</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.293443326404642</v>
+        <v>1.30610341058626</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.230124476587477</v>
+        <v>-2.217117345169875</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.238167826880478</v>
+        <v>-3.225188684482013</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.217066792876246</v>
+        <v>-1.203955988501306</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.488224874128264</v>
+        <v>-1.47444293622533</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.136244805476565</v>
+        <v>-4.121200582710316</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.4548410339236</v>
+        <v>-2.598137459118384</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.0471314838993564</v>
+        <v>0.06020146049489483</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.657694555829359</v>
+        <v>-1.644289428176528</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7228467405457906</v>
+        <v>-0.7093894468355728</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.4035632983001491</v>
+        <v>-0.3901110095800391</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8855838001566596</v>
+        <v>0.8991398465082625</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2806042777320314</v>
+        <v>0.2701746420338793</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>321</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7760630142338769</v>
+        <v>-0.7626276485452408</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.319097854812817</v>
+        <v>-3.303892508380876</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.536988331541309</v>
+        <v>-1.523981200123707</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.258814725176904</v>
+        <v>3.271793867575369</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.098805908453116</v>
+        <v>2.111916712828055</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.271242000335988</v>
+        <v>-2.256792290680323</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.11187351765647</v>
+        <v>-1.097928564769852</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9562259708471359</v>
+        <v>-0.9430449615518981</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7063898303696945</v>
+        <v>-0.69292330620641</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6241703428578305</v>
+        <v>0.6375754705106615</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.138215380213637</v>
+        <v>-1.124758086503419</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.415358702618924</v>
+        <v>-1.401906413898814</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2779809148099304</v>
+        <v>-0.2644248684583275</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.208944940789017</v>
+        <v>-2.219374576487169</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>298</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.1940804058928265</v>
+        <v>0.2072240213162218</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.097590708955337</v>
+        <v>-5.080078635653969</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.82341382888449</v>
+        <v>-4.810406697466888</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.023986576226861</v>
+        <v>-4.011007433828397</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.552571830260341</v>
+        <v>-2.539461025885402</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9170685238026124</v>
+        <v>-0.9029675558539552</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-3.014791351084547</v>
+        <v>-2.999079732307621</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-5.829141916791265</v>
+        <v>-5.815960907496027</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.552382847158555</v>
+        <v>-4.536017658211634</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.73136709258921</v>
+        <v>-4.717961964936379</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.600549947108128</v>
+        <v>-4.58709265339791</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.901737259561315</v>
+        <v>-4.888284970841205</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.986421400707599</v>
+        <v>-4.972865354355996</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.716565840243391</v>
+        <v>-1.726995475941543</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>232</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.584066268484463</v>
+        <v>1.596492615342939</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.791617404141178</v>
+        <v>2.559862405090264</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.965521798783378</v>
+        <v>1.97852893020098</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8049077127911133</v>
+        <v>0.8178868551895775</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.275884095280659</v>
+        <v>3.288994899655599</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.713975227516585</v>
+        <v>2.725415653199633</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4779773356161954</v>
+        <v>0.4918756625337366</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4420814654872984</v>
+        <v>0.4552624747825362</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8109589718646859</v>
+        <v>0.8241252690382765</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.03916621316315627</v>
+        <v>-0.02576108551032519</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6181494280365172</v>
+        <v>0.6316067217467349</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.945636033657756</v>
+        <v>1.959088322377866</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.491859956597445</v>
+        <v>-1.478303910245842</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.673173107079776</v>
+        <v>-1.683602742777929</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>198</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.779013896202287</v>
+        <v>1.791234553902278</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.86545062279167</v>
+        <v>-2.852540813215619</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.250802160915661</v>
+        <v>-2.237795029498059</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.119783251729601</v>
+        <v>-2.106804109331136</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.16839607775831</v>
+        <v>-4.15528527338337</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.575661077282888</v>
+        <v>-1.840918977679266</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.374688271263459</v>
+        <v>2.386975163929108</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.412844894822662</v>
+        <v>2.4260259041179</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.857284294052221</v>
+        <v>2.868290973523244</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5180934162282824</v>
+        <v>-0.5046882885754513</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2872542695551417</v>
+        <v>0.3007115632653594</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.836788942052088</v>
+        <v>1.850241230772198</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.416534331107187</v>
+        <v>1.430090377458789</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1511041482319584</v>
+        <v>0.1406745125338063</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-2.842795769043839</v>
+        <v>-3.464434756935006</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.476105063429635</v>
+        <v>-1.752043382696563</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.072941087176801</v>
+        <v>-3.356111153609234</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.6974833924083015</v>
+        <v>0.4364815037065881</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-2.866163905481542</v>
+        <v>-3.145480632711738</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1343256485528315</v>
+        <v>-0.3988664038684604</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4910332786170244</v>
+        <v>-1.099717741298278</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.8548828715501671</v>
+        <v>0.599877336772991</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.284129847361967</v>
+        <v>-1.890541849969196</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2899873918525202</v>
+        <v>0.6470732290397194</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.996652319464367</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.092503987240868</v>
+        <v>-1.352518069548111</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.9066979921251601</v>
+        <v>-0.5531567277394913</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.5551445522723668</v>
+        <v>0.2823350200480164</v>
       </c>
     </row>
     <row r="22">
@@ -1404,49 +1404,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>5.900722263731595</v>
+        <v>6.214736143378694</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>10.8584917164608</v>
+        <v>11.1252891807496</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.9745719149737013</v>
+        <v>1.310227940922147</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-3.274736996214415</v>
+        <v>-2.907373002446022</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.8934501820895093</v>
+        <v>-0.5471118309040648</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.975570288169465</v>
+        <v>-4.597563888225423</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-5.060304005441743</v>
+        <v>-4.682274247491634</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.607779375026119</v>
+        <v>-2.250792166640643</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.668779261208464</v>
+        <v>-2.311774323163419</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.329123424338583</v>
+        <v>-1.712417757174492</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.8039497413568952</v>
+        <v>-0.4678435531158343</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.420214437886386</v>
+        <v>1.74044764271779</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.189821194956323</v>
+        <v>-1.578253935233391</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9400998626800785</v>
+        <v>-0.6278806038474301</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>113</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5.913641325807724</v>
+        <v>5.926163615483347</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7622447039939075</v>
+        <v>0.7751545135699587</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.022243254034485</v>
+        <v>3.035250385452088</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.4976291300048743</v>
+        <v>0.5106082724033385</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.8441636671450397</v>
+        <v>0.8572744715199789</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.51326165177646</v>
+        <v>-1.500218755482095</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.252862625685971</v>
+        <v>-4.239796371385495</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.06517876783024</v>
+        <v>-2.051997758535002</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.435913167286934</v>
+        <v>-7.422714428332171</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.091348086828091</v>
+        <v>-2.07794295917526</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.181057163358048</v>
+        <v>-3.16759986964783</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.26171825380024</v>
+        <v>-2.24826596508013</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.79701711253275</v>
+        <v>-1.783461066181147</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2226157241682714</v>
+        <v>0.2121860884701192</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>88</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.064538514920187</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.849533521371228</v>
+        <v>3.862443330947279</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.09078973067998</v>
+        <v>-1.077782599262378</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.857645220109404</v>
+        <v>5.870624362507868</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.319224005037235</v>
+        <v>5.332334809412174</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.343938670025629</v>
+        <v>3.356981566319995</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.395568589117048</v>
+        <v>4.408634843417524</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.928385190335547</v>
+        <v>3.941566199630785</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.594658031425965</v>
+        <v>1.607856770380728</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.880896482761678</v>
+        <v>1.894301610414509</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.085234067534948</v>
+        <v>5.098691361245166</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.983253588516675</v>
+        <v>3.996705877236785</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.699362613935477</v>
+        <v>4.71291866028708</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.949083946211765</v>
+        <v>4.938654310513613</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>95</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-8.282912004420503</v>
+        <v>-8.27038971474488</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.500119360229242</v>
+        <v>5.513126491646844</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.419846177047233</v>
+        <v>1.432825319445698</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.381732932761807</v>
+        <v>-4.368622128386868</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.189554152940886</v>
+        <v>-6.176511256646521</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.116393133371055</v>
+        <v>-3.103326879070579</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.425681795310517</v>
+        <v>-0.4125007860152792</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.697207997282227</v>
+        <v>-4.684009258327464</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.494701603362884</v>
+        <v>-4.481296475710053</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.59419176978566</v>
+        <v>-2.580734476075442</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.717703349282246</v>
+        <v>-5.704251060562136</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.032694802332472</v>
+        <v>-4.019138755980869</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4275528457333806</v>
+        <v>0.4171232100352285</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>53</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.883920170356063</v>
+        <v>7.896442460031686</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6119691989011855</v>
+        <v>0.6248790084772367</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.556484413355726</v>
+        <v>-3.543477281938124</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.234146077742281</v>
+        <v>2.247125220140745</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.964652495820346</v>
+        <v>-3.951541691445406</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1063743475556365</v>
+        <v>0.1194172438500019</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.02164063028335761</v>
+        <v>0.03470688458383364</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.332335221328272</v>
+        <v>-2.319154212033034</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.040627156640312</v>
+        <v>7.053825895595075</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.96408687727282</v>
+        <v>9.977492004925651</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.872541100125048</v>
+        <v>7.885998393835266</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.793716710300615</v>
+        <v>9.807168999020725</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.713084740865149</v>
+        <v>3.726640787216752</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.849598525971565</v>
+        <v>5.839168890273413</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>45</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.074639525021205</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.216123044285276</v>
+        <v>-5.203213234709224</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.388769528659715</v>
+        <v>-3.375762397242113</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.258516396052215</v>
+        <v>-3.245537253653751</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.019159833346663</v>
+        <v>-6.006049028971724</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.721717895630945</v>
+        <v>-5.70867499933658</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.806451612903153</v>
+        <v>-5.793385358602677</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.829190567240346</v>
+        <v>-1.816009557945108</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.334634897866955</v>
+        <v>-6.321436158912192</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.740315638450504</v>
+        <v>-2.726910510797673</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.7228467405458048</v>
+        <v>-0.709389446835587</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.108718194145332</v>
+        <v>-1.095162147793729</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.869426497567197</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>30</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.826771653543311</v>
+        <v>-5.814249363867688</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.297039159503342</v>
+        <v>2.310018301901806</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.091951277764608</v>
+        <v>5.105062082139547</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.389393215480077</v>
+        <v>5.402436111774442</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.304659498207798</v>
+        <v>5.317725752508274</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>4.850657108721627</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.223523786756104</v>
+        <v>-5.210325047801341</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.5930176948828247</v>
+        <v>0.6064228225356558</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.721597703898489</v>
+        <v>3.735054997608707</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.422647527910776</v>
+        <v>0.436099816630886</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.335726250299111</v>
+        <v>3.349282296650713</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2521142492420623</v>
+        <v>0.2416846135439101</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>38</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.03287746926371</v>
+        <v>8.045399758939332</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.6844617510363</v>
+        <v>11.69737156061235</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.28959304443971</v>
+        <v>11.30260017585731</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>11.41984617704721</v>
+        <v>11.43282531944568</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>18.77616180408026</v>
+        <v>18.7892726084552</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>13.8104458470592</v>
+        <v>13.82348874335356</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.35729107715526</v>
+        <v>16.37035733145574</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>15.89010767837376</v>
+        <v>15.903288687669</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>18.46068673955995</v>
+        <v>18.47388547851472</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>17.61056155453194</v>
+        <v>17.62396668218477</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>25.30054507231964</v>
+        <v>25.31400236602985</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>22.70334928229657</v>
+        <v>22.71680157101668</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.01993677661489</v>
+        <v>17.03349282296649</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>12.00650021415434</v>
+        <v>11.99607057845619</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>32</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-14.99343832020998</v>
+        <v>-14.98091603053435</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.269988066825768</v>
+        <v>5.282897876401819</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>11.12511936022922</v>
+        <v>11.13812649164682</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.25537249283668</v>
+        <v>11.26835163523514</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.466951277764466</v>
+        <v>4.480062082139405</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.01439321548017</v>
+        <v>11.02743611177453</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23.42965949820789</v>
+        <v>23.44272575250837</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>19.83747609942639</v>
+        <v>19.85065710872163</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>22.90147621324409</v>
+        <v>22.91467495219885</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.92635102821616</v>
+        <v>18.93975615586899</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.47159770389858</v>
+        <v>12.4850549976088</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>15.63098086124401</v>
+        <v>15.64443314996412</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.33572625029911</v>
+        <v>18.34928229665071</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.3354475825754</v>
+        <v>12.32501794687725</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>24</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>18.33989501312337</v>
+        <v>18.35241730279899</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>16.72832140015911</v>
+        <v>16.74123120973516</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>16.33345269356239</v>
+        <v>16.34645982497999</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20.63037249283668</v>
+        <v>20.64335163523514</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.92528461109785</v>
+        <v>15.93839541547279</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.05605988214683</v>
+        <v>12.06910277844119</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.97132616487455</v>
+        <v>11.98439241917502</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>11.51732377538828</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.109809546577424</v>
+        <v>3.123008285532187</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.7596843615495</v>
+        <v>14.77308948920233</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.221597703898581</v>
+        <v>6.235054997608799</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.00239291696577</v>
+        <v>10.01594896331737</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.25211424924206</v>
+        <v>10.2416846135439</v>
       </c>
     </row>
     <row r="32">
@@ -1927,98 +1927,98 @@
         <v>17</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.2124440327312</v>
+        <v>12.22496632240682</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>16.48322336094342</v>
+        <v>16.49613317051947</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>16.08835465434683</v>
+        <v>16.10136178576443</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.466881046999852</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.797833630705682</v>
+        <v>9.810944435080621</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.09527556842134</v>
+        <v>10.10831846471571</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.01054185114906</v>
+        <v>10.02360810544954</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.221347429985371</v>
+        <v>-2.208166420690134</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-8.164700257344151</v>
+        <v>-8.151501518389388</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.132472501195601</v>
+        <v>-3.119067373542769</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.427480056839755</v>
+        <v>8.440937350549973</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.579510273008722</v>
+        <v>2.592962561728832</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.159255662063821</v>
+        <v>2.172811708415423</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.291329935516572</v>
+        <v>8.28090029981842</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 1.715</t>
+          <t>X ≈ 1.714</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.480916030534353</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20.89498806682581</v>
+        <v>20.90789787640186</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.750119360229263</v>
+        <v>1.763126491646865</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.880372492836678</v>
+        <v>1.893351635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.908048722235492</v>
+        <v>-4.894937917860553</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.597563888225466</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.55465949820789</v>
+        <v>1.567725752508366</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-5.149342891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.47352378675591</v>
+        <v>-11.46032504780115</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.32364897178384</v>
+        <v>-12.31024384413101</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.278402296101419</v>
+        <v>-6.264945002391201</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-12.49401913875599</v>
+        <v>-12.48056685003588</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.91427374970089</v>
+        <v>-12.90071770334929</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-12.6645524174246</v>
+        <v>-12.67498205312275</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.99343832020998</v>
+        <v>-14.98091603053435</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.35501193317427</v>
+        <v>-10.34210212359822</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.00011936022922</v>
+        <v>8.013126491646823</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.13037249283672</v>
+        <v>8.143351635235184</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.591951277764508</v>
+        <v>7.605062082139447</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.889393215480169</v>
+        <v>7.902436111774534</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.05465949820789</v>
+        <v>14.06772575250837</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.58747609942643</v>
+        <v>13.60065710872167</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>19.77647621324409</v>
+        <v>19.78967495219885</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.6763510282162</v>
+        <v>12.68975615586903</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.47159770389854</v>
+        <v>12.48505499760876</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.255980861244012</v>
+        <v>6.269433149964122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.08572625029911</v>
+        <v>12.09928229665071</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.164552417424602</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0428165206488913</v>
+        <v>-0.0430808281940287</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.06571977414284191</v>
+        <v>0.06542043187609892</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.0231790052258134</v>
+        <v>-0.02345887420687376</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.04716117024029387</v>
+        <v>0.04686468719903303</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.08340844154288618</v>
+        <v>0.08310014948936839</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.02076303451983108</v>
+        <v>-0.0210444837831929</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07877427232266854</v>
+        <v>0.0784679400083661</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01578582097011605</v>
+        <v>0.01549227355679506</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1392907746904584</v>
+        <v>0.1389665985105211</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.08470879947715559</v>
+        <v>0.08439334130753906</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.01590227490811458</v>
+        <v>0.01560240718847439</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01514956540049184</v>
+        <v>0.01484991848037964</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.02440318842579359</v>
+        <v>0.02409892256758184</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.06783505811356605</v>
+        <v>0.06804802758157535</v>
       </c>
     </row>
     <row r="7">
@@ -2266,49 +2266,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4022</v>
+        <v>4023</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.09640058933153028</v>
+        <v>0.09589269097208586</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.01001037718769737</v>
+        <v>0.009508780986706711</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.04909958348517307</v>
+        <v>-0.04959041464970682</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.06985661982080416</v>
+        <v>0.06933725388130796</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.06590315074888053</v>
+        <v>0.06537954245690969</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.02003606491685161</v>
+        <v>-0.02053585547924541</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1073400641051308</v>
+        <v>0.106807638364451</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.100633994163239</v>
+        <v>0.1000986574930351</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.0781896475624464</v>
+        <v>0.07765906342030604</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.0863112865370752</v>
+        <v>0.08577055865022487</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.02995509113247863</v>
+        <v>-0.03046909578414869</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.03129548070430133</v>
+        <v>-0.03180908606071853</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.009850038516852067</v>
+        <v>0.009322058082126716</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.07475638416665475</v>
+        <v>0.07514223223643057</v>
       </c>
     </row>
     <row r="8">
@@ -2318,49 +2318,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3942</v>
+        <v>3943</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.136809530068227</v>
+        <v>0.1360245510079992</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1069789598184343</v>
+        <v>0.1061780989612515</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1223502753983468</v>
+        <v>-0.1230991597572171</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.2241462210067553</v>
+        <v>0.223311149405184</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.1805588727012193</v>
+        <v>0.179726724002272</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.08678496022567117</v>
+        <v>0.08598041557200276</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.269198505300082</v>
+        <v>0.2683461627388013</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2466476221018397</v>
+        <v>0.2457938868371343</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1490053566804761</v>
+        <v>0.1481750788773439</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04802403201844641</v>
+        <v>0.04720673873771375</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.0553351224639016</v>
+        <v>-0.04187782875368384</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.05740656269107802</v>
+        <v>-0.05819676131597618</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.006906263015629577</v>
+        <v>-0.007715674951718654</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.130348648024416</v>
+        <v>0.1309398337654031</v>
       </c>
     </row>
     <row r="9">
@@ -2373,46 +2373,46 @@
         <v>3846</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3333251652672047</v>
+        <v>0.3321511201008533</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1362332030125373</v>
+        <v>0.1350762996383281</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.07705314301336585</v>
+        <v>-0.06404601159576373</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.3008447294739369</v>
+        <v>0.2996421670120526</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2178272185898393</v>
+        <v>0.2166344744591129</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1920931116380018</v>
+        <v>0.1909126235835146</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3033611341466056</v>
+        <v>0.3021494285208277</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.4478657098159999</v>
+        <v>0.4466062128504191</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2454291880427348</v>
+        <v>0.2442204067443043</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1373697392348703</v>
+        <v>0.136170809025657</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.1193586370577577</v>
+        <v>-0.10590134334754</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.04438305869359738</v>
+        <v>-0.04553566500469231</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.06999562107393587</v>
+        <v>0.0688040018755629</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1117086330174146</v>
+        <v>0.1012789973192625</v>
       </c>
     </row>
     <row r="10">
@@ -2425,98 +2425,98 @@
         <v>3752</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3648440514996807</v>
+        <v>0.3633157610658628</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04392423703853865</v>
+        <v>0.04243656292135967</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2445614908346556</v>
+        <v>-0.2315543594170535</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.0984575992196568</v>
+        <v>0.111436741618121</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07998000880999712</v>
+        <v>0.07846633745859322</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.01951562101503157</v>
+        <v>0.01802536423529233</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1888756280987636</v>
+        <v>0.1873372479846864</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1889137991068921</v>
+        <v>0.1873619263953046</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.009498849728771575</v>
+        <v>0.007992311091292947</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.02676564732993114</v>
+        <v>-0.02828645398454199</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2315189716475103</v>
+        <v>-0.2180616779372926</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1289112250869309</v>
+        <v>-0.1304070205206926</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.07879661277245731</v>
+        <v>0.0772332692059976</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1686032328952223</v>
+        <v>0.1581735971970701</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.7255</t>
+          <t>X &gt; 0.7256</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3618</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2774467087395678</v>
+        <v>0.2754235505020333</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.03177791790133</v>
+        <v>0.02976167568497345</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2527763926665756</v>
+        <v>-0.2397692612489735</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.09810553199829286</v>
+        <v>0.1110846743967571</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1264340363851915</v>
+        <v>0.1243671014444701</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02515480488414568</v>
+        <v>0.02312576694694712</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.09350851835693419</v>
+        <v>0.09145643683508098</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1660238630928674</v>
+        <v>0.1639333990887266</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1558629195921455</v>
+        <v>-0.1578678418375929</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1620467618390862</v>
+        <v>-0.1640825627170415</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2563028485876089</v>
+        <v>-0.2428455548773911</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09591192681898519</v>
+        <v>-0.09797016495301136</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.07978374062525972</v>
+        <v>0.07766030162446214</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.08074885399607012</v>
+        <v>0.07031921829791798</v>
       </c>
     </row>
     <row r="12">
@@ -2529,46 +2529,46 @@
         <v>3457</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.06849605693052752</v>
+        <v>-0.07110362072194931</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2499729496339498</v>
+        <v>-0.2526102067390497</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3271979946654255</v>
+        <v>-0.3141908632478234</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1206987995072026</v>
+        <v>0.1336779419056668</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08906277400944873</v>
+        <v>0.08629222941060277</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1423547872802331</v>
+        <v>0.1395822700645439</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.04454389127148062</v>
+        <v>0.0417939408932213</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.08880317203934851</v>
+        <v>-0.09153942307028728</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3073872916720433</v>
+        <v>-0.3100648569945577</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3188774275386095</v>
+        <v>-0.3054722998857784</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.4079569519718618</v>
+        <v>-0.394499658261644</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2706318087010331</v>
+        <v>-0.2733661559930809</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2569841922811662</v>
+        <v>-0.2434281459295633</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.09404330547783246</v>
+        <v>-0.1044729411759846</v>
       </c>
     </row>
     <row r="13">
@@ -2581,46 +2581,46 @@
         <v>3246</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.04954037984723669</v>
+        <v>-0.05313483815574216</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3227241102960079</v>
+        <v>-0.3263474356178548</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3485891268556855</v>
+        <v>-0.3355819954380834</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.08916708078255908</v>
+        <v>0.1021462231810233</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.09041328945321681</v>
+        <v>0.08661189763760291</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.0970855231724812</v>
+        <v>0.09330046120548019</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.06314598040091113</v>
+        <v>-0.0668896321070207</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.04067806986974176</v>
+        <v>0.03686825061143395</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3728924347386666</v>
+        <v>-0.3765812054366151</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.2066948602963095</v>
+        <v>-0.1932897326434784</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4422458439917776</v>
+        <v>-0.4287885502815598</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2058182761558669</v>
+        <v>-0.2096244416589172</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1947728254864671</v>
+        <v>-0.1812167791348642</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.006665787726511496</v>
+        <v>-0.01709542342466364</v>
       </c>
     </row>
     <row r="14">
@@ -2633,46 +2633,46 @@
         <v>2978</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.08056968750219795</v>
+        <v>-0.08560614778728848</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3001175315651139</v>
+        <v>-0.3052388528206933</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4267998486209734</v>
+        <v>-0.4137927172033713</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.03868627091244292</v>
+        <v>0.05166541331090713</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2562705265907965</v>
+        <v>0.2508884314522248</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03160644906193966</v>
+        <v>-0.03686636978146396</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06446801857062923</v>
+        <v>-0.06972812203037648</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1244851628704922</v>
+        <v>0.1191134845605504</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3209045792340817</v>
+        <v>-0.3261357225242136</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.09648308864078814</v>
+        <v>-0.08307796098795706</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3348159965715283</v>
+        <v>-0.3213587028613105</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.0989553375471246</v>
+        <v>-0.08550304882701454</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.0826753615208986</v>
+        <v>-0.0691193151692957</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.03443153092359807</v>
+        <v>-0.04486116662175021</v>
       </c>
     </row>
     <row r="15">
@@ -2685,46 +2685,46 @@
         <v>2677</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4894103002225378</v>
+        <v>0.4821849758018359</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2776810918164472</v>
+        <v>0.2703139837843693</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.07988809967383759</v>
+        <v>-0.06688096825623546</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1622635782525634</v>
+        <v>0.1752427206510276</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.295233635093858</v>
+        <v>0.3083444394687973</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.01625888712195689</v>
+        <v>0.00892622740302329</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2720482285558319</v>
+        <v>-0.2792891728647717</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.3454962680119991</v>
+        <v>-0.352777008486278</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3486638689374573</v>
+        <v>-0.3559561157623179</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.07813160159333421</v>
+        <v>-0.06472647394050313</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.02139818702409713</v>
+        <v>-0.007940893313879371</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.0243702780910624</v>
+        <v>-0.01091798937095234</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2578486469739616</v>
+        <v>-0.2442926006223587</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1949035567596766</v>
+        <v>-0.2053331924578288</v>
       </c>
     </row>
     <row r="16">
@@ -2737,46 +2737,46 @@
         <v>2353</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.89926736257204</v>
+        <v>0.8891560338997309</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7528582407757085</v>
+        <v>0.7425034743662025</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.02385178953747413</v>
+        <v>-0.01084465811987201</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4033890392940407</v>
+        <v>0.4163681816925049</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4165164029236053</v>
+        <v>0.4296272072985445</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.06901085922271477</v>
+        <v>-0.07910822424582875</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2579731981827678</v>
+        <v>-0.2680127873897717</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.192260519095278</v>
+        <v>-0.2024214475416457</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1873996898583385</v>
+        <v>-0.1975807827204363</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.152445375857468</v>
+        <v>0.1658505035102991</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2451846142258205</v>
+        <v>0.2586419079360383</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3645656466243778</v>
+        <v>0.3780179353444879</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.1993046608388482</v>
+        <v>0.2128607071904511</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3640281180620093</v>
+        <v>0.3535984823638572</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>2002</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8963921882646062</v>
+        <v>0.8823126690172174</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6580803361524517</v>
+        <v>0.6436904985354133</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3629622529972636</v>
+        <v>0.3759693844148657</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.041843814532434</v>
+        <v>1.054822956930899</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7029238463430616</v>
+        <v>0.7160346507180009</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1798123771568214</v>
+        <v>0.1655283811012183</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4219835121869195</v>
+        <v>0.4075461117898058</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2044256750629359</v>
+        <v>0.2176066843581737</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2285187917509219</v>
+        <v>-0.2427763708166282</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4698075716726962</v>
+        <v>0.4832126993255272</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4149043972052695</v>
+        <v>0.4283616909154873</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.499237604500756</v>
+        <v>0.5126898932208661</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.07898299355585436</v>
+        <v>0.09253903990745727</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3786543757821974</v>
+        <v>0.3682247400840453</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1681</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.215760492846407</v>
+        <v>1.196426792715947</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.417553387490855</v>
+        <v>1.397512119725256</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7257725668800035</v>
+        <v>0.7387796982976056</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.6184960082761108</v>
+        <v>0.631475150674575</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4363693300210372</v>
+        <v>0.4494801343959764</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.6478602386530738</v>
+        <v>0.62808931842536</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.7148854197298817</v>
+        <v>0.6950281886343319</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4260611172623001</v>
+        <v>0.4392421265575379</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.137265607100943</v>
+        <v>-0.156817318906981</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.4403308021602399</v>
+        <v>0.453735929813071</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.7114846759390332</v>
+        <v>0.724941969649251</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8648446328085555</v>
+        <v>0.8782969215286656</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1471480230534254</v>
+        <v>0.1607040694050283</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8727765534260783</v>
+        <v>0.8623469177279262</v>
       </c>
     </row>
     <row r="19">
@@ -2893,46 +2893,46 @@
         <v>1383</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.435905587504514</v>
+        <v>1.409573883010317</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.821394993232694</v>
+        <v>2.793261971571255</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.921475781585592</v>
+        <v>1.934482913003194</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.618828481292667</v>
+        <v>1.631807623691131</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.080407266220497</v>
+        <v>1.093518070595437</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9850610855162714</v>
+        <v>0.9579916673300914</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.518532330577827</v>
+        <v>1.491010951064325</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.773892284397483</v>
+        <v>1.787073293692721</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8140756347914433</v>
+        <v>0.7867847787884514</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.554695207536483</v>
+        <v>1.568100335189314</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.856087942510293</v>
+        <v>1.86954523622051</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.107390839552032</v>
+        <v>2.120843128272142</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.253296749214513</v>
+        <v>1.266852795566116</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.430711501592029</v>
+        <v>1.420281865893877</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1151</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.406041749114117</v>
+        <v>1.3718978222795</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.827397078957482</v>
+        <v>2.840306888533533</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.912597696451016</v>
+        <v>1.925604827868618</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.782885491103578</v>
+        <v>1.795864633502042</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6378784874698766</v>
+        <v>0.6509892918448159</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6365744817420946</v>
+        <v>0.6017428708733235</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.728270609319004</v>
+        <v>1.692400514000127</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.042337210537504</v>
+        <v>2.055518219832742</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.8147038413935306</v>
+        <v>0.7792582855321868</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.875960063837354</v>
+        <v>1.889365191490185</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.105611604854268</v>
+        <v>2.119068898564485</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.139994762199699</v>
+        <v>2.153447050919809</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.806621124321701</v>
+        <v>1.820177170673304</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.056342456597989</v>
+        <v>2.045912820899837</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>953</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.328551208585836</v>
+        <v>1.284774346034688</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.010171312899068</v>
+        <v>4.023081122475119</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.777606271223945</v>
+        <v>2.790613402641547</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.593723278176995</v>
+        <v>2.606702420575459</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.636453895565559</v>
+        <v>1.649564699940498</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.096199498202679</v>
+        <v>1.109242394497045</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.593967674308516</v>
+        <v>1.548092244654967</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.965358699007105</v>
+        <v>1.978539708302343</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3903272100961317</v>
+        <v>0.3452305077544082</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.37336047207765</v>
+        <v>2.386765599730481</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.483402530761118</v>
+        <v>2.496859824471336</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.202990305105502</v>
+        <v>2.216442593825612</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.88766748849428</v>
+        <v>1.901223534845883</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.452184203771623</v>
+        <v>2.44175456807347</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.201993151871235</v>
+        <v>2.271935680492263</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.158947457688711</v>
+        <v>5.22348723001398</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.002657431295169</v>
+        <v>4.068259571494693</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.990778584207241</v>
+        <v>3.057800304436668</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.579260922434557</v>
+        <v>2.646253463635006</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.353860220556314</v>
+        <v>1.422714945741589</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.030547823080987</v>
+        <v>2.098460860239669</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.197882190796953</v>
+        <v>2.265105777923154</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.7409432183202327</v>
+        <v>0.8099537861659059</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.809599759180628</v>
+        <v>2.748374660304989</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.366267754660001</v>
+        <v>3.430872488103098</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.893036698807471</v>
+        <v>2.958279791282251</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.472782087862569</v>
+        <v>2.411386225674789</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.849406973438342</v>
+        <v>2.890607300489407</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>651</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.423612371034267</v>
+        <v>1.436134660709889</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.959504195858031</v>
+        <v>3.972414005434082</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.639904306465738</v>
+        <v>4.65291143788334</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.309327945985686</v>
+        <v>4.32230708838415</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.310077237825951</v>
+        <v>3.32318804220089</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.685860189366494</v>
+        <v>2.698903085660859</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.522785458269333</v>
+        <v>3.535851712569809</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.209211890517018</v>
+        <v>3.222392899812256</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.458503863013675</v>
+        <v>1.471702601968438</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.680575298569465</v>
+        <v>3.693980426222296</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.24387112939781</v>
+        <v>4.257328423108028</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.202985469538945</v>
+        <v>3.216437758259055</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.243560351681595</v>
+        <v>3.257116398033197</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.646891514987068</v>
+        <v>3.636461879288916</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>538</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4805393749573099</v>
+        <v>0.4930616646329327</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.631047546379669</v>
+        <v>4.64395735595572</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.979673263574902</v>
+        <v>4.992680394992504</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.109926396182402</v>
+        <v>5.122905538580866</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.82801075731841</v>
+        <v>3.841121561693349</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.567831877190208</v>
+        <v>3.580874773484574</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.15596061344953</v>
+        <v>5.169026867750006</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.317030002772114</v>
+        <v>4.330211012067352</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.326662086850042</v>
+        <v>3.339860825804806</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.892893779145524</v>
+        <v>4.906298906798355</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.803382090515683</v>
+        <v>5.816839384225901</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.350776400277468</v>
+        <v>4.364228688997578</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.302269001228474</v>
+        <v>4.315825047580077</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.366116727556815</v>
+        <v>4.355687091858663</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>450</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1732283464566891</v>
+        <v>0.1857506361323118</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.783876955714661</v>
+        <v>4.796786765290712</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.166786026895849</v>
+        <v>6.179793158313451</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.963705826170013</v>
+        <v>4.976684968568478</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.536395722208951</v>
+        <v>3.54950652658389</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.61161543770239</v>
+        <v>3.624658333996756</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.30465949820789</v>
+        <v>5.317725752508366</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.393031654981939</v>
+        <v>4.406212664277177</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.665365102132981</v>
+        <v>3.678563841087744</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.48190658377171</v>
+        <v>5.495311711424542</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.943819926120803</v>
+        <v>5.95727721983102</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.422647527910684</v>
+        <v>4.436099816630794</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.224615139188003</v>
+        <v>4.238171185539606</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.252114249242069</v>
+        <v>4.241684613543917</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>355</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.43613914457876</v>
+        <v>2.448661434254383</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.486537362600416</v>
+        <v>4.499447172176467</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.345189782764386</v>
+        <v>6.358196914181988</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.912062633681742</v>
+        <v>5.925041776080207</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.655331559454645</v>
+        <v>5.668442363829584</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.234463638015377</v>
+        <v>6.247506534309743</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.55818062496845</v>
+        <v>7.571246879268926</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.682546521961598</v>
+        <v>5.695727531256836</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.903236776624368</v>
+        <v>5.916435515579131</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.151703140892224</v>
+        <v>8.165108268545055</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.228639957419716</v>
+        <v>8.242097251129934</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.13626255138486</v>
+        <v>7.14971484010497</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.434317799594886</v>
+        <v>6.447873845946489</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.275588427645815</v>
+        <v>5.265158791947663</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>302</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.48007161356486</v>
+        <v>1.492593903240483</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.166511245633721</v>
+        <v>5.179421055209772</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.082900817182818</v>
+        <v>8.09590794860042</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.557524810717474</v>
+        <v>6.570503953115939</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.343606906903574</v>
+        <v>7.356717711278513</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.309923016804674</v>
+        <v>7.32296591309904</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.880818438605246</v>
+        <v>8.893884692905722</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.089131728565455</v>
+        <v>7.102312737860693</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.703628531124885</v>
+        <v>5.716827270079648</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.833635796428084</v>
+        <v>7.847040924080915</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.291134127739639</v>
+        <v>8.304591421449857</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.669888146012227</v>
+        <v>6.683340434732337</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.911885190696466</v>
+        <v>6.925441237048069</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.174851556085336</v>
+        <v>5.164421920387184</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>257</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.203059734264734</v>
+        <v>1.215582023940357</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.984482230249895</v>
+        <v>6.997392039825947</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.09155904894513</v>
+        <v>10.10456618036273</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.276286889723835</v>
+        <v>8.289266032122299</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.683390966480459</v>
+        <v>9.696501770855399</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.591727845830363</v>
+        <v>9.604770742124728</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.45251942038687</v>
+        <v>11.46558567468735</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.650705671410819</v>
+        <v>8.663886680706057</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.811495668497002</v>
+        <v>7.824694407451766</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.685105892029384</v>
+        <v>9.698511019682215</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.869457626077562</v>
+        <v>9.88291491978778</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.958315491594206</v>
+        <v>7.971767780314316</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.316270997380819</v>
+        <v>8.329827043732422</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.231361979462555</v>
+        <v>6.220932343764403</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>227</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.132112340582978</v>
+        <v>2.144634630258601</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.45005414612092</v>
+        <v>8.462963955696971</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.5794145144142</v>
+        <v>11.5924216458318</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.066495840854301</v>
+        <v>9.079474983252766</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.29018916322705</v>
+        <v>10.30329996760199</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.1471024665815</v>
+        <v>10.16014536287587</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.26501192111538</v>
+        <v>12.27807817541586</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.154656716166478</v>
+        <v>9.167837725461716</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.53418546434542</v>
+        <v>9.547384203300183</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.88670345112365</v>
+        <v>10.90010857877648</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.68195012680607</v>
+        <v>10.69540742051629</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.954218746706559</v>
+        <v>8.967671035426669</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.9744927701229</v>
+        <v>8.988048816474503</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.021570930593022</v>
+        <v>7.01114129489487</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.9457151189434683</v>
+        <v>0.958237408619091</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.799749971587673</v>
+        <v>7.812659781163724</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>11.63768549779532</v>
+        <v>11.65069262921292</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.59333545579964</v>
+        <v>8.606314598198104</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.584014769827995</v>
+        <v>8.597125574202934</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.410557236644195</v>
+        <v>9.42360013293856</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11.44222563577403</v>
+        <v>11.45529189007451</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.800439062389351</v>
+        <v>7.813620071684589</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.73943917620705</v>
+        <v>7.752637915161813</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.534816636681768</v>
+        <v>9.548221764334599</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.742761725062607</v>
+        <v>7.756219018772825</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.189843295106442</v>
+        <v>6.203295583826552</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.356890271463136</v>
+        <v>7.370446317814739</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.019310016437828</v>
+        <v>6.008880380739676</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>157</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.194459768961998</v>
+        <v>4.206982058637621</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.315370232430858</v>
+        <v>8.328280042006909</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.74215757678968</v>
+        <v>11.75516470820728</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.050754658441768</v>
+        <v>8.063733800840232</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.423161468847312</v>
+        <v>9.436272273222251</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.083660731403732</v>
+        <v>9.096703627698098</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>8.998927014131453</v>
+        <v>9.011993268431929</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.347030239553774</v>
+        <v>5.360211248849012</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.64908767821224</v>
+        <v>4.662286417167003</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.620618544139724</v>
+        <v>7.634023671792555</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.778922544662912</v>
+        <v>6.79237983837313</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.265535001371397</v>
+        <v>4.278987290091507</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.119165740744968</v>
+        <v>5.132721787096571</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.731944397862023</v>
+        <v>4.721514762163871</v>
       </c>
     </row>
     <row r="32">
@@ -3569,98 +3569,98 @@
         <v>133</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.641900025654685</v>
+        <v>1.654422315330308</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.797243705923513</v>
+        <v>6.810153515499564</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.91365319481565</v>
+        <v>10.92666032623325</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.780748432686302</v>
+        <v>5.793727575084766</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.249846014606611</v>
+        <v>8.26295681898155</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.547287952322272</v>
+        <v>8.560330848616637</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.462554235049993</v>
+        <v>8.475620489350469</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.235972340027892</v>
+        <v>4.24915334932313</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.926852153093712</v>
+        <v>4.940050892048475</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.332366065810149</v>
+        <v>6.34577119346298</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.879492440740684</v>
+        <v>6.892949734450902</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.906356801093636</v>
+        <v>3.919809089813747</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.237981889396856</v>
+        <v>4.251537935748459</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.735823522425022</v>
+        <v>3.72539388672687</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 1.693</t>
+          <t>X &gt; 1.692</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.09276857634174718</v>
+        <v>0.1052908660173699</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.377746687515426</v>
+        <v>5.390656497091477</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.15529177402229</v>
+        <v>10.16829890543989</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.975200079043574</v>
+        <v>5.988179221442039</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.022985760523127</v>
+        <v>8.036096564898067</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.320427698238788</v>
+        <v>8.333470594533154</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.235693980966509</v>
+        <v>8.248760235266985</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.182303685633286</v>
+        <v>5.195484694928524</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.845441730485469</v>
+        <v>6.858640469440232</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.719454476492025</v>
+        <v>7.732859604144856</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.6526321866572</v>
+        <v>6.666089480367418</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.100808447450909</v>
+        <v>4.114260736171019</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.542622802023246</v>
+        <v>4.556178848374849</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.068206203265056</v>
+        <v>3.057776567566904</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.5065616797900248</v>
+        <v>0.5190839694656475</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.894988066825761</v>
+        <v>2.907897876401812</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11.50011936022918</v>
+        <v>11.51312649164678</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.630372492836678</v>
+        <v>6.643351635235142</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.09195127776451</v>
+        <v>10.10506208213945</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.38939321548017</v>
+        <v>10.40243611177453</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.30465949820789</v>
+        <v>9.317725752508366</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.837476099426389</v>
+        <v>6.850657108721627</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.776476213244088</v>
+        <v>9.789674952198851</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.92635102821616</v>
+        <v>10.93975615586899</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.721597703898581</v>
+        <v>8.735054997608799</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.755980861244012</v>
+        <v>6.769433149964122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.335726250299111</v>
+        <v>7.349282296650713</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.585447582575398</v>
+        <v>5.575017946877246</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.458942632170981</v>
+        <v>3.471464921846604</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.418797590635293</v>
+        <v>5.431707400211344</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>12.16678602689583</v>
+        <v>12.17979315831344</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10.56814175395499</v>
+        <v>10.58125255832993</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.86558369167065</v>
+        <v>10.87862658796502</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.399897593445985</v>
+        <v>8.412963847746461</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5.551761813712098</v>
+        <v>5.564942823007335</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.871714308482183</v>
+        <v>7.884913047436946</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.59301769488282</v>
+        <v>10.60642282253565</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.007311989612873</v>
+        <v>8.020769283323091</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.851218956482107</v>
+        <v>6.864671245202217</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.430964345537205</v>
+        <v>6.444520391888808</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>6.680685677813493</v>
+        <v>6.670256042115341</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Volume Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Volume Ratio-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.077990251218594</v>
+        <v>1.090512540894217</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.724059552221846</v>
+        <v>-1.711149742645794</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2620241221339441</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.988675126210936</v>
+        <v>-1.975695983812471</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.717572531759302</v>
+        <v>-3.704461727384363</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.532250358337308</v>
+        <v>2.545293254631673</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.123911930363541</v>
+        <v>-1.110845676063065</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>1.993514251578766</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.842571405803525</v>
+        <v>-2.829372666848762</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1212680194028835</v>
+        <v>-0.1078628917500524</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.245407227708107</v>
+        <v>3.258864521418325</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.279790385053538</v>
+        <v>3.293242673773648</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.859535774108636</v>
+        <v>2.873091820460239</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="7">
@@ -3963,46 +3963,46 @@
         <v>150</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.16010498687664</v>
+        <v>-3.147582697201017</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.561654733492432</v>
+        <v>0.5745645430684831</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8334526935625135</v>
+        <v>0.8464598249801156</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.702960840496658</v>
+        <v>-1.689981698098194</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.574715388902156</v>
+        <v>-1.561604584527217</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>1.402436111774541</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.162523900573611</v>
+        <v>-1.149342891278373</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1098095465774236</v>
+        <v>0.1230082855321868</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.07364897178383245</v>
+        <v>-0.06024384413100137</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.054931037231917</v>
+        <v>3.068388330942135</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.089314194577348</v>
+        <v>3.102766483297458</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.002392916965775</v>
+        <v>2.015948963317378</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2521142492420623</v>
+        <v>0.2416846135439101</v>
       </c>
     </row>
     <row r="8">
@@ -4015,46 +4015,46 @@
         <v>230</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.709888536660188</v>
+        <v>-2.697366246984565</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.291159119321421</v>
+        <v>-1.27824930974537</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.77717563728546</v>
+        <v>1.790182768703062</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.720276857812678</v>
+        <v>-3.707297715414214</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.959996774183551</v>
+        <v>-2.946885969808612</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.9309531048661484</v>
+        <v>-0.917910208571783</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.613089419541026</v>
+        <v>-3.60002316524055</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.21447195252167</v>
+        <v>-3.201290943226432</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.110969674201797</v>
+        <v>-1.097770935247034</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6363077381728743</v>
+        <v>0.6497128658257054</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.417249877811628</v>
+        <v>2.176613439167241</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.451633035157059</v>
+        <v>2.465085323877169</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.596595815516501</v>
+        <v>1.610151861868104</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7623785043811253</v>
+        <v>-0.7728081400792775</v>
       </c>
     </row>
     <row r="9">
@@ -4064,49 +4064,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.165170843006329</v>
+        <v>-4.152648553330707</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.21747393925326</v>
+        <v>-1.204564129677209</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.6830461894974746</v>
+        <v>0.5283240600358425</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.454993360821859</v>
+        <v>-3.442014218423395</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.469024331991591</v>
+        <v>-2.455913527616651</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.866704345495435</v>
+        <v>-1.85366144920107</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.866072209109184</v>
+        <v>-2.853005954808708</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.552767803012635</v>
+        <v>-4.539586793717397</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.869865250170541</v>
+        <v>-1.856666511215778</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5858440937350551</v>
+        <v>-0.572438966082224</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.437194034173814</v>
+        <v>2.271640363462453</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.554145998858687</v>
+        <v>1.567598287578797</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2164601952532408</v>
+        <v>0.2300162416048437</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2795830922712312</v>
+        <v>-0.1558689032756604</v>
       </c>
     </row>
     <row r="10">
@@ -4116,101 +4116,101 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.436834546625072</v>
+        <v>-3.424312256949449</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.09557797091007814</v>
+        <v>-0.08266816133402699</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>2.001301393326109</v>
+        <v>1.881051019948664</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.8151251374950803</v>
+        <v>-0.9287523836773914</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6426458786335942</v>
+        <v>-0.629535074258655</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1287297083711678</v>
+        <v>0.1417726046655332</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.140838132123868</v>
+        <v>-1.127771877823392</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.13408788161626</v>
+        <v>-1.120906872321022</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7006468293578294</v>
+        <v>0.7138455683125926</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.035355767552652</v>
+        <v>1.048760895205483</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.866490815537531</v>
+        <v>2.739794334101695</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.950755208037364</v>
+        <v>1.964207496757474</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.105322449824051</v>
+        <v>0.1188784961756539</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.7002667031388867</v>
+        <v>-0.605504618443419</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.7255</t>
+          <t>X &lt; 0.7256</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.955803911607823</v>
+        <v>-1.943281621932201</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.01685186610892231</v>
+        <v>0.02976167568497345</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.514482017320745</v>
+        <v>1.427104986270429</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.5926490898971366</v>
+        <v>-0.6762174850521134</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7713580747534792</v>
+        <v>-0.7582472703785399</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.06565220828592544</v>
+        <v>0.07869510458029083</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1989376240942633</v>
+        <v>-0.1858713697937873</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6661210228757639</v>
+        <v>-0.6529400135805261</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.611008587344806</v>
+        <v>1.624207326299569</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.660163977856442</v>
+        <v>1.673569105509273</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.28015626245714</v>
+        <v>2.188292407680741</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.233458338721491</v>
+        <v>1.246910627441601</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.09248300705586843</v>
+        <v>0.1060390534074713</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.0836425284237805</v>
+        <v>0.1515945234538236</v>
       </c>
     </row>
     <row r="12">
@@ -4220,49 +4220,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.2111386562116593</v>
+        <v>0.223660945887282</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.373490147269592</v>
+        <v>1.386399956845644</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.472341582451399</v>
+        <v>1.407717337693931</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.5448709007655523</v>
+        <v>-0.6066483647648582</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.3878818237653903</v>
+        <v>-0.374771019390451</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.5076860612931284</v>
+        <v>-0.494643164998763</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1029905135069171</v>
+        <v>0.1160567678073932</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.7484635820411256</v>
+        <v>0.7616445913363634</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.939202221589007</v>
+        <v>1.95240096054377</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>2.004345457185522</v>
+        <v>1.936974514700708</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.438473575586173</v>
+        <v>2.370152490645012</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.775506663196587</v>
+        <v>1.788958951916698</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.715614518455531</v>
+        <v>1.647748126497291</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.9281049252327449</v>
+        <v>0.9772525837487507</v>
       </c>
     </row>
     <row r="13">
@@ -4272,49 +4272,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.08166897592735722</v>
+        <v>0.09419126560297997</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.259794933778558</v>
+        <v>1.272704743354609</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.139217104590074</v>
+        <v>1.092525633277681</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.2836060017869784</v>
+        <v>-0.3287214045070712</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.284392808256996</v>
+        <v>-0.2712820038820567</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.2020046339821988</v>
+        <v>-0.1889617376878334</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4659498207885377</v>
+        <v>0.4790160750890138</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1062933037274689</v>
+        <v>0.1194743130227067</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.658196643351616</v>
+        <v>1.671395382306379</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.084585689141882</v>
+        <v>1.036530349417376</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.911252876312375</v>
+        <v>1.8620732968553</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.083567068140567</v>
+        <v>1.097019356860677</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.048779108983034</v>
+        <v>1.000144365616229</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.3889033061175127</v>
+        <v>0.4250718843098227</v>
       </c>
     </row>
     <row r="14">
@@ -4324,49 +4324,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1293760011888594</v>
+        <v>0.1418982908644821</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8491928961346744</v>
+        <v>0.8621027057107256</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1.000119360229185</v>
+        <v>0.9669150012221337</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.07438146879801621</v>
+        <v>-0.1066483647648582</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.6128026838701857</v>
+        <v>-0.5996918794952464</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1850562680239562</v>
+        <v>0.1980991643183216</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.350531057840918</v>
+        <v>0.363597312141394</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1166523409405826</v>
+        <v>-0.1034713316453448</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.073390308323319</v>
+        <v>1.086589047278082</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.5206749013380261</v>
+        <v>0.48687875803747</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.115081413171765</v>
+        <v>1.080630957542027</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.5285561120801319</v>
+        <v>0.4945793487945309</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4905379657802769</v>
+        <v>0.4563057080219508</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.369367180565348</v>
+        <v>0.3951016288856195</v>
       </c>
     </row>
     <row r="15">
@@ -4376,49 +4376,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9298987327182928</v>
+        <v>-0.9173764430426701</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.4123971627151519</v>
+        <v>-0.3994873531391008</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.09399419378443241</v>
+        <v>0.07067805518636305</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.2723590194884338</v>
+        <v>-0.295396700317454</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5080487222354861</v>
+        <v>-0.5311804228572257</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.05605988214683322</v>
+        <v>0.06910277844119861</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6379928315412258</v>
+        <v>0.6510590858417018</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7708094327597266</v>
+        <v>0.7839904420549644</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.8431428799107508</v>
+        <v>0.856341618865514</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.3639761116050906</v>
+        <v>0.339756155868983</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2636537786649384</v>
+        <v>0.2393912217582326</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2690069133482211</v>
+        <v>0.244733550498168</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6886674267696975</v>
+        <v>0.6639115551677506</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5754141377593456</v>
+        <v>0.59373452441735</v>
       </c>
     </row>
     <row r="16">
@@ -4428,49 +4428,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.207176689120764</v>
+        <v>-1.194654399445142</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.9030414898244743</v>
+        <v>-0.8901316802484232</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.009190606912106603</v>
+        <v>-0.02600870266083177</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5066138085331886</v>
+        <v>-0.5231324830562087</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5220838099547862</v>
+        <v>-0.5387735342989046</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1591300575854362</v>
+        <v>0.1721729538798016</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.458168270137719</v>
+        <v>0.471234524438195</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.37475680118078</v>
+        <v>0.3879378104760178</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4234060378054991</v>
+        <v>0.4366047767602623</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.01221178034116122</v>
+        <v>-0.02954208974503558</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1313111874296311</v>
+        <v>-0.1486531757318517</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2857544490250703</v>
+        <v>-0.3030147095309346</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.07086715629429818</v>
+        <v>-0.08838931235533209</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2848108011519273</v>
+        <v>-0.2711358992766009</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8642506194297965</v>
+        <v>-0.8517283297541738</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5483345582316019</v>
+        <v>-0.5354247486555508</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3676492348121485</v>
+        <v>-0.3794847979355964</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9474869467590921</v>
+        <v>-0.9590358762432771</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6341516634119628</v>
+        <v>-0.6459714502445664</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.106930313931592</v>
+        <v>-0.09388741763722663</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.283575795909762</v>
+        <v>-0.270509541609286</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.08206413045866867</v>
+        <v>-0.09419583245484375</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3626831097958174</v>
+        <v>0.3758818487505806</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2778808025106088</v>
+        <v>-0.290128901602273</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.226860648609474</v>
+        <v>-0.2391860327499842</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3047926194189756</v>
+        <v>-0.3170831868973565</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.08376862708399813</v>
+        <v>0.07119758210190952</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1933542607425736</v>
+        <v>-0.1836186261305812</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.8534383202099747</v>
+        <v>-0.8409160305343519</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9050119331742295</v>
+        <v>-0.8921021235981783</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5182880027160053</v>
+        <v>-0.5268735083532263</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.4064569707341832</v>
+        <v>-0.415071734112594</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2824980614425385</v>
+        <v>-0.2912549715034629</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3855367004189105</v>
+        <v>-0.3724938041245451</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3901743023527828</v>
+        <v>-0.3771080480523068</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.194575182624888</v>
+        <v>-0.2034077691318004</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2251941619620368</v>
+        <v>0.2383929009168</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.16182532448925</v>
+        <v>-0.1708207672079354</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3441601148664546</v>
+        <v>-0.3531213550966115</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4477896963171588</v>
+        <v>-0.4567095926180755</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.03717087309205169</v>
+        <v>0.02798265766153918</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4530911568866642</v>
+        <v>-0.4458488267985175</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2789</v>
+        <v>2790</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7421874267146293</v>
+        <v>-0.7296651370390066</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.353046243395816</v>
+        <v>-1.340136433819765</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9782503215727587</v>
+        <v>-0.9843717213625141</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.793089595861467</v>
+        <v>-0.7992654545038604</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5252222463857592</v>
+        <v>-0.5315616660722853</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4424493605484585</v>
+        <v>-0.4294064642540931</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6702957790729727</v>
+        <v>-0.6572295247724966</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.7960242584834205</v>
+        <v>-0.8022945907417025</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2843684538997948</v>
+        <v>-0.2711697149450316</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6493739986366833</v>
+        <v>-0.6558057625275708</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.7984596026916719</v>
+        <v>-0.8048662340417607</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9233455450619772</v>
+        <v>-0.929707251182009</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.4993991977295664</v>
+        <v>-0.5059667180393674</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5880913202571563</v>
+        <v>-0.5826881463127194</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.563382233110012</v>
+        <v>-0.5508599434343893</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.035705002481158</v>
+        <v>-1.040304037158066</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7527693819299515</v>
+        <v>-0.757500571059488</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6708164107300334</v>
+        <v>-0.6755654991326381</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2334534133488049</v>
+        <v>-0.2383989482436419</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.2002995496338045</v>
+        <v>-0.1872566533394391</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5823573501568262</v>
+        <v>-0.5692910958563502</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7011888047375265</v>
+        <v>-0.7059996471422636</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2003909381108357</v>
+        <v>-0.1871921991560725</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6025745916185556</v>
+        <v>-0.6075009492202312</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6897779574770837</v>
+        <v>-0.6946970685069047</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7031656819250216</v>
+        <v>-0.7080800775491127</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5755907583044646</v>
+        <v>-0.5805886924329826</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.671421003985337</v>
+        <v>-0.667205746041347</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3219</v>
+        <v>3220</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4191349146372261</v>
+        <v>-0.4066126249616033</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.14743992945791</v>
+        <v>-1.150925653009942</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8443663894610367</v>
+        <v>-0.8479760168697936</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7594632679318423</v>
+        <v>-0.7630919831043883</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4753146862776489</v>
+        <v>-0.4790717883284756</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2850253891709968</v>
+        <v>-0.2888224127139978</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.4007668583812602</v>
+        <v>-0.3877006040807842</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.5099184415165396</v>
+        <v>-0.513683976549693</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.01260567261198986</v>
+        <v>0.0005930663427733407</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.5973846217993568</v>
+        <v>-0.6011867721707134</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6297368708996842</v>
+        <v>-0.6335456849850658</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5470306258717912</v>
+        <v>-0.5508648016187436</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4530936254772868</v>
+        <v>-0.4569890476523</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6208276581825984</v>
+        <v>-0.6175286369736881</v>
       </c>
     </row>
     <row r="22">
@@ -4743,46 +4743,46 @@
         <v>3384</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5358286646315236</v>
+        <v>-0.5527441141375249</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.1603711793462</v>
+        <v>-1.176907777308429</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9505433790933537</v>
+        <v>-0.9669913286772243</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.6866575601980927</v>
+        <v>-0.7031421773753479</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5903357838328986</v>
+        <v>-0.6066974227234994</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2768803694254913</v>
+        <v>-0.2933186052065935</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4045708173332514</v>
+        <v>-0.4209943890428036</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4427598887741979</v>
+        <v>-0.4590774045527084</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.0745122789365027</v>
+        <v>-0.09082076925290039</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5541684523033155</v>
+        <v>-0.5407633246504844</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6834805364320928</v>
+        <v>-0.6995478958071999</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5736115782125779</v>
+        <v>-0.5896926622036318</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4752043257717915</v>
+        <v>-0.4616482794201886</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.563488587637373</v>
+        <v>-0.5739182233355251</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3521</v>
+        <v>3522</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2863075901590406</v>
+        <v>-0.2885539371821579</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.694312810615493</v>
+        <v>-0.6965163850582812</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8758715797481713</v>
+        <v>-0.8780424865587051</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7870729900293725</v>
+        <v>-0.7892644463050615</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6020997137369051</v>
+        <v>-0.6043686740202858</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4592891307935574</v>
+        <v>-0.4615865511149764</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5853631775290751</v>
+        <v>-0.5876298723145297</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5268561943076691</v>
+        <v>-0.52916148538268</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1753105139255098</v>
+        <v>-0.1777194339650308</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5842872696561798</v>
+        <v>-0.5866193404441091</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.6881639306076579</v>
+        <v>-0.690476917284812</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4960770439504287</v>
+        <v>-0.4984442620676646</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5030017451580164</v>
+        <v>-0.5053870192732219</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5781423066606095</v>
+        <v>-0.5760325925889589</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3634</v>
+        <v>3635</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.09420607452859286</v>
+        <v>-0.09604760948172242</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6491699145236538</v>
+        <v>-0.6509175883637397</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7550246726926346</v>
+        <v>-0.7567583136192653</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.7472345324103031</v>
+        <v>-0.7489666089349498</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5572389500696957</v>
+        <v>-0.5590432965652781</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4919906395445466</v>
+        <v>-0.4938032513876962</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6991855992927967</v>
+        <v>-0.700945307348853</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5746118126615301</v>
+        <v>-0.5764233636760707</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4007702830461</v>
+        <v>-0.4026327401088352</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6310981196672927</v>
+        <v>-0.6329286476484555</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7656170335223749</v>
+        <v>-0.7674188891421636</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5509498318252923</v>
+        <v>-0.5528104574045827</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5432283576788848</v>
+        <v>-0.5451071422931761</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.553242566021197</v>
+        <v>-0.5515295084184899</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.04363912342282816</v>
+        <v>-0.0451558592281387</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5431479803086674</v>
+        <v>-0.5445786965566839</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7629398414852631</v>
+        <v>-0.7643239636290673</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5914924589318105</v>
+        <v>-0.5929194603983987</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4186356962371036</v>
+        <v>-0.4201254848487679</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4014915030184909</v>
+        <v>-0.4029779863224974</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5789554119556968</v>
+        <v>-0.5803975718884118</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4683178919899191</v>
+        <v>-0.469804140943161</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3536552597905214</v>
+        <v>-0.3551748332088778</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5717702814993473</v>
+        <v>-0.5732569914344694</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.6273955846920174</v>
+        <v>-0.628874148929043</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.443804315984778</v>
+        <v>-0.4453319507070148</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4193100107806629</v>
+        <v>-0.4208573381505758</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4231499456352381</v>
+        <v>-0.4217588460317003</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3817</v>
+        <v>3818</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2480075108105027</v>
+        <v>-0.2491227650684209</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3834136046289132</v>
+        <v>-0.3845303220316012</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6075086439505455</v>
+        <v>-0.6085763028165232</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.541563749650912</v>
+        <v>-0.5426462749007044</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.517039835669884</v>
+        <v>-0.5181414715579606</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5452473073956412</v>
+        <v>-0.5463354512155334</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6419932214573834</v>
+        <v>-0.6430585612171242</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4672584022738491</v>
+        <v>-0.4683805481821466</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4616190248511458</v>
+        <v>-0.4627446135871764</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6693045593263633</v>
+        <v>-0.6703955971399083</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6763080552637248</v>
+        <v>-0.6774024742572067</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5749958342260015</v>
+        <v>-0.5761165882557719</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.509218747081718</v>
+        <v>-0.5103668261563072</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4019770964919331</v>
+        <v>-0.4008856675805887</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3870</v>
+        <v>3871</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1370128759658371</v>
+        <v>-0.1379706134385756</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.369823885775979</v>
+        <v>-0.3707526515404922</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6477806655373755</v>
+        <v>-0.6486457906819183</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5036481257200265</v>
+        <v>-0.5045483905314114</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5641456544345118</v>
+        <v>-0.5650410106440589</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5363416994244261</v>
+        <v>-0.5372390622393795</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.6329211053515706</v>
+        <v>-0.633795650276582</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4927612586747401</v>
+        <v>-0.4936812972623841</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3590076577236516</v>
+        <v>-0.3599638506907326</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5238296635752704</v>
+        <v>-0.5247599731632704</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.5593214801964308</v>
+        <v>-0.5602470158140207</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4330687255328485</v>
+        <v>-0.4340267002811657</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4514088569083299</v>
+        <v>-0.4523705959112689</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3163612029543188</v>
+        <v>-0.3154496325595986</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3915</v>
+        <v>3916</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1003629637945025</v>
+        <v>-0.1011756385771108</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4253582535205496</v>
+        <v>-0.4261143435574439</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.6791980111411746</v>
+        <v>-0.679896171964117</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5352326027047312</v>
+        <v>-0.5359657361352106</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6267031564862506</v>
+        <v>-0.6274219942936767</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.59582218090015</v>
+        <v>-0.5965445202336213</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6922808383550816</v>
+        <v>-0.6929803397679564</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5080990089643223</v>
+        <v>-0.5088533451284434</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4276054194089696</v>
+        <v>-0.4283816660107931</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5492805104416618</v>
+        <v>-0.5500397624983577</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5611996416858958</v>
+        <v>-0.5619595469178691</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4360027997210167</v>
+        <v>-0.4367945172130092</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.458962207310698</v>
+        <v>-0.4597552320702505</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.322598394436092</v>
+        <v>-0.3218155566978282</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3945</v>
+        <v>3946</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1437667689214379</v>
+        <v>-0.1444674324035162</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4532555520774366</v>
+        <v>-0.4539010119256233</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6828937843613119</v>
+        <v>-0.6834871045119257</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5137488725236281</v>
+        <v>-0.5143834507102554</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5833142761049928</v>
+        <v>-0.5839391820830571</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5503993471305009</v>
+        <v>-0.5510287339513127</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6467575058406894</v>
+        <v>-0.6473640527028692</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.4675099800471614</v>
+        <v>-0.46816880220954</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.4640301158698392</v>
+        <v>-0.464691031096514</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5406026309380607</v>
+        <v>-0.5412565023588556</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5286555889079025</v>
+        <v>-0.5293157291574673</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.4294764481048645</v>
+        <v>-0.4301615815455051</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.430112573826591</v>
+        <v>-0.4308038447224831</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.318227956081131</v>
+        <v>-0.3175314702540319</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3983</v>
+        <v>3984</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.06601089278254335</v>
+        <v>-0.06660529748456412</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3378029219101464</v>
+        <v>-0.3383483698444252</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5689842952540474</v>
+        <v>-0.5694767624208126</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4001809757333206</v>
+        <v>-0.4007144639135873</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.3990306861633499</v>
+        <v>-0.399571025799446</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4136636624952743</v>
+        <v>-0.4141971547585328</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4848141860026374</v>
+        <v>-0.4853311254670771</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.311684091097554</v>
+        <v>-0.3122501594488014</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2837043283807859</v>
+        <v>-0.2842784195735248</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3676043266872782</v>
+        <v>-0.3681676154449463</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2824163452735178</v>
+        <v>-0.2830036931361235</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2088873947158447</v>
+        <v>-0.2094930918823366</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2636713400623307</v>
+        <v>-0.2642685189076275</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.200643303691237</v>
+        <v>-0.2000824547291771</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4015</v>
+        <v>4016</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1846001871414487</v>
+        <v>-0.1850609796532368</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2932413843785966</v>
+        <v>-0.2936910014531975</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4760356323192596</v>
+        <v>-0.4764439081545575</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3075157059210838</v>
+        <v>-0.3079648078845736</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3603350045416533</v>
+        <v>-0.3607764271773206</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3227618926480886</v>
+        <v>-0.323210011485898</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2945448777244764</v>
+        <v>-0.2950010682721498</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1513326546148974</v>
+        <v>-0.151829216489709</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.09914567730317714</v>
+        <v>-0.09965605998716853</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.213982388056543</v>
+        <v>-0.2144726998524007</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.180841320491659</v>
+        <v>-0.1813421161010851</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.08270472501438775</v>
+        <v>-0.08322986646196284</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1154689688243948</v>
+        <v>-0.1159902948354699</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1007292542863709</v>
+        <v>-0.100280857903627</v>
       </c>
     </row>
     <row r="32">
@@ -5260,101 +5260,101 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4039</v>
+        <v>4040</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07487958378352033</v>
+        <v>-0.07529056791406674</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1923977638333341</v>
+        <v>-0.1927931403800187</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3764238496473666</v>
+        <v>-0.3767772358279231</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1834086877017285</v>
+        <v>-0.1838088585920161</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2637799475319369</v>
+        <v>-0.2641648874826856</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2493515337167693</v>
+        <v>-0.2497378012689495</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.2217863742587483</v>
+        <v>-0.222180350778018</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.08217779426953342</v>
+        <v>-0.08261031589528045</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08010143265106962</v>
+        <v>-0.08053518377148094</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.1250959171214632</v>
+        <v>-0.125525743240793</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.142825848798104</v>
+        <v>-0.1432531893810562</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.04505848545234414</v>
+        <v>-0.0455099475123788</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.05536285861178669</v>
+        <v>-0.0558154514314424</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.039211986624899</v>
+        <v>-0.03884343926137035</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 1.693</t>
+          <t>X &lt; 1.692</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.02354399728050538</v>
+        <v>-0.0239135735318996</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.1227110482184841</v>
+        <v>-0.123067962870735</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3076013184037265</v>
+        <v>-0.3079157895724904</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1640200305278157</v>
+        <v>-0.1643690433977625</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2217018587668562</v>
+        <v>-0.2220407215988729</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.2060792254647126</v>
+        <v>-0.206419976786357</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1789732854495014</v>
+        <v>-0.1793214915861228</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.091130498308722</v>
+        <v>-0.09150385608270994</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1139448653079924</v>
+        <v>-0.1143132309621535</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.137688380650836</v>
+        <v>-0.1380571905973937</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1069314904842642</v>
+        <v>-0.1073095344109092</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.03406349558200361</v>
+        <v>-0.03445943441626298</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04608296833534808</v>
+        <v>-0.04647916219601456</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.004296007168193228</v>
+        <v>-0.003981313660098351</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03321800197252855</v>
+        <v>-0.03353472852749206</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04036942582849434</v>
+        <v>-0.04069453485889341</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2995377546373419</v>
+        <v>-0.2998020098223719</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1560067330329886</v>
+        <v>-0.1563054796313779</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2400751863374282</v>
+        <v>-0.2403568301584471</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2233518825590508</v>
+        <v>-0.2236359293918397</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1721730587913797</v>
+        <v>-0.1724703259230083</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1110280692837691</v>
+        <v>-0.1113433815946294</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.158525013147873</v>
+        <v>-0.1588292165113074</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.1855233584374218</v>
+        <v>-0.185826380309571</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1311630322977351</v>
+        <v>-0.1314808218220165</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.08299802928127065</v>
+        <v>-0.08332758623219405</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.09663318991695036</v>
+        <v>-0.09696218052160077</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.05404161192361556</v>
+        <v>-0.05375691194916499</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.09158511367498789</v>
+        <v>-0.09183753224083802</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.08062168927178703</v>
+        <v>-0.08088534720218377</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.267140947162865</v>
+        <v>-0.2673613132312624</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1236538614825022</v>
+        <v>-0.1239086721569009</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2094888003414184</v>
+        <v>-0.2097256191782648</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1916614720198311</v>
+        <v>-0.1919012082157039</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1165859230375332</v>
+        <v>-0.1168445599916339</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.05749214678758108</v>
+        <v>-0.05776779970327794</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.08059683830734343</v>
+        <v>-0.0808673047625561</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1352325494964575</v>
+        <v>-0.1354942716902485</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08187333007844444</v>
+        <v>-0.08214930346647265</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.05820006785134524</v>
+        <v>-0.05848178525954495</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.04896438310758811</v>
+        <v>-0.04925071068424813</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.05447413953810809</v>
+        <v>-0.0542312583073965</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
+++ b/workspaces/btc_daily_14days/volume/volume_ratio_7.xlsx
@@ -568,573 +568,573 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ 0.5277</t>
+          <t>X ≈ 0.5274</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>66</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.514148519182612</v>
+        <v>-7.829304371218754</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.473489697452543</v>
+        <v>2.65577254179636</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.569377295513114</v>
+        <v>2.258434521785901</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.322940400115769</v>
+        <v>-0.6343189868084806</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>1.163251696331315</v>
+        <v>1.894302205499407</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.05204769085494831</v>
+        <v>0.6597722789545912</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.648965491605956</v>
+        <v>-0.9161999295127714</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.14165140183006</v>
+        <v>-5.093795685282274</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>3.875939532873282</v>
+        <v>3.949100664225547</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0004456841916962162</v>
+        <v>-1.413972522431116</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>2.823869929292307</v>
+        <v>1.409672288265483</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>2.858928331644925</v>
+        <v>1.468158850954637</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.9248159805224745</v>
+        <v>-0.4413109914157758</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.3643759925166989</v>
+        <v>-1.707528748100863</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ 0.5717</t>
+          <t>X ≈ 0.5714</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-1.882106360548299</v>
+        <v>-2.502910333261752</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.755080228683767</v>
+        <v>-5.29939968415308</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>3.573471859836481</v>
+        <v>2.823479673867133</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.519651121752084</v>
+        <v>-7.99942326312955</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.570507167960223</v>
+        <v>-6.055133142903458</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-5.270456564917993</v>
+        <v>-5.784425992830542</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-7.855022381735964</v>
+        <v>-8.282236360937858</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-7.08085495880426</v>
+        <v>-7.529503382952036</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3.397899048418275</v>
+        <v>-3.912529836372578</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>1.986484832588111</v>
+        <v>2.573178756765166</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.5318388304522017</v>
+        <v>1.151144835133159</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>1.268773458082698</v>
+        <v>1.209577998756863</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.8490693249875818</v>
+        <v>0.8148425062209057</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.674982053122754</v>
+        <v>-2.594446708190787</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ 0.6157</t>
+          <t>X ≈ 0.6153</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>97</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-7.640292817354045</v>
+        <v>-8.156551000128282</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.039620661905246</v>
+        <v>-1.511768486882815</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.46452604459153</v>
+        <v>-2.934068313075969</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-2.803174352821657</v>
+        <v>-2.804518105982901</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-1.283646556997752</v>
+        <v>-1.23562263183679</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.074527543317501</v>
+        <v>-5.081068626592121</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-1.071935901155115</v>
+        <v>-1.024373145460409</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-7.716311328080984</v>
+        <v>-7.667173664470646</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.659972663147151</v>
+        <v>-4.615433364251253</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-3.480172790410833</v>
+        <v>-3.38002801706665</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.496621523081032</v>
+        <v>2.595792935732788</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.5602027037199875</v>
+        <v>-0.436567279978938</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-3.041681418020936</v>
+        <v>-2.893031057062814</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>1.306976709763838</v>
+        <v>-0.5828802007725855</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ 0.6596</t>
+          <t>X ≈ 0.6593</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.9117822086301928</v>
+        <v>0.06504004736785873</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>3.832781535404997</v>
+        <v>4.22919237388858</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.622031871654073</v>
+        <v>6.954540798718952</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7.811841699756847</v>
+        <v>7.086698272034575</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.731600964096963</v>
+        <v>4.520543130264187</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.091689188206374</v>
+        <v>6.874062017295508</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4.884865400559335</v>
+        <v>3.694521922301995</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>10.79431432752681</v>
+        <v>9.471214527949918</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>9.673239714086066</v>
+        <v>9.43406993988922</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.70046496662453</v>
+        <v>5.491729853357739</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>4.370966479851695</v>
+        <v>3.207312853207945</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.342095461548979</v>
+        <v>2.225257354981657</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.2676493068882664</v>
+        <v>-1.29333211755489</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-2.169662904186097</v>
+        <v>-2.086316626889428</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ 0.7036</t>
+          <t>X ≈ 0.7032</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2.736405446289304</v>
+        <v>2.786216144944945</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3846585183036737</v>
+        <v>0.4510454498399952</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.009752009955249719</v>
+        <v>0.05771737075844641</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1209425565950824</v>
+        <v>0.1881205863990729</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.160854290159975</v>
+        <v>-0.3002078187940285</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.1196855089794298</v>
+        <v>0.7282527226553484</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>2.77611914902397</v>
+        <v>3.694236445809139</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.8199321636730588</v>
+        <v>1.715995411623943</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4.486216440171262</v>
+        <v>5.461505662878075</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.638208481792716</v>
+        <v>4.640037496065887</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.4511029994455384</v>
+        <v>1.409390584882935</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-1.006202120848165</v>
+        <v>-0.04629345942653629</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0657033939074978</v>
+        <v>1.073462549897009</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>2.530241827473922</v>
+        <v>3.595501554928923</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ 0.7475</t>
+          <t>X ≈ 0.7471</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>7.716072189764944</v>
+        <v>8.203178175766269</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.092864765994591</v>
+        <v>6.62387704427325</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.358215074838043</v>
+        <v>0.7251925789877163</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3740390882014495</v>
+        <v>-0.9804191727871299</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.941912645674627</v>
+        <v>-0.2444858211765251</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-2.477434054652541</v>
+        <v>-3.647055594277717</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1.157812017400509</v>
+        <v>-0.03290320559406723</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>5.649458530788635</v>
+        <v>4.402960724348652</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.110114030197359</v>
+        <v>1.915139770049024</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.871844899347167</v>
+        <v>1.705639555788615</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.013478888596929</v>
+        <v>1.502151119007145</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>3.668141269988048</v>
+        <v>2.787168032078434</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.972087402209965</v>
+        <v>5.459606595192582</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>3.823465151846328</v>
+        <v>2.029225295400828</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ 0.7915</t>
+          <t>X ≈ 0.7911</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.3475333278780255</v>
+        <v>-0.62173774396922</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.881754935159563</v>
+        <v>0.6209216688857637</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.01488788125273288</v>
+        <v>0.2285351668901754</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.6187583162194485</v>
+        <v>0.8298620830020411</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08137448976677319</v>
+        <v>0.3417831565861675</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.8515763532707652</v>
+        <v>1.555904756921855</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.713769665816301</v>
+        <v>1.966585345371797</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.066948469377692</v>
+        <v>-1.795536128707461</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7132150815973901</v>
+        <v>0.993071133325401</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.031276154239052</v>
+        <v>-1.713835175930257</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.1329967564143004</v>
+        <v>0.4380187830564708</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-1.253961439067403</v>
+        <v>-0.9177725820808433</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-1.20048073652486</v>
+        <v>-0.3698953859872702</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.448678735587322</v>
+        <v>-0.5926059350654143</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ 0.8355</t>
+          <t>X ≈ 0.8351</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.3076844158844025</v>
+        <v>0.518210895923076</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.5609047474460169</v>
+        <v>0.07200245567998564</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.5334908755208758</v>
+        <v>1.190250465713156</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6630859686779687</v>
+        <v>0.9436419770161422</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.73881913855621</v>
+        <v>-1.055824491713942</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.539706515978267</v>
+        <v>1.862200023648072</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.0353485015407955</v>
+        <v>0.6675491767221402</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.8770358788679928</v>
+        <v>-0.553620270391221</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.9371283998885218</v>
+        <v>-0.2130526827776009</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-1.417956359472264</v>
+        <v>-1.035500346359278</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.622542601093052</v>
+        <v>-0.8615344787122652</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.588853948574666</v>
+        <v>-1.560500588969958</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-1.426837106334283</v>
+        <v>-1.577315354231942</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.2914358573250055</v>
+        <v>0.1864106458377606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.8794</t>
+          <t>X ≈ 0.879</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-5.135363084159714</v>
+        <v>-5.43151367789914</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-5.424026040833141</v>
+        <v>-6.032986367911107</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.499117474450841</v>
+        <v>-3.496419033198855</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.047392565923289</v>
+        <v>-0.7600142765910078</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.2601073607748887</v>
+        <v>-0.2700188484573687</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.4441314284620788</v>
+        <v>-0.6507676783717002</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.794042419775842</v>
+        <v>1.571725309838676</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4.315960161923847</v>
+        <v>4.369092277966139</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.0609224577455052</v>
+        <v>-0.2353410482007092</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.2462903557588376</v>
+        <v>-0.07857137225110478</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-3.108798822989201</v>
+        <v>-3.220650147812364</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.7488392752850501</v>
+        <v>-0.5509577159666179</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.488817180371647</v>
+        <v>1.667267481545203</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.382326916976915</v>
+        <v>1.590153961345877</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.9234</t>
+          <t>X ≈ 0.9229</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>324</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-2.473379529458484</v>
+        <v>-2.35420721994786</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.158889322817643</v>
+        <v>-3.321448994328705</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.4738360230428</v>
+        <v>-0.7807400487293279</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-1.575893729443422</v>
+        <v>-2.188816683777588</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5724529454182417</v>
+        <v>-1.138578137292605</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.6482628469393035</v>
+        <v>0.055835329414748</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.36118218219395</v>
+        <v>-0.9292649297578919</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.444711066827942</v>
+        <v>-1.70222133176577</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.506132531341166</v>
+        <v>-2.047104434916214</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.739256189810092</v>
+        <v>-2.25354008227697</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.943957348070214</v>
+        <v>-2.458235134204742</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.835505121640814</v>
+        <v>-3.326287192697933</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.564297950262862</v>
+        <v>-4.031286345198261</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-4.264488225962261</v>
+        <v>-4.709773417012954</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.9673</t>
+          <t>X ≈ 0.9669</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9281885595258998</v>
+        <v>0.7482171498817607</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.30610341058626</v>
+        <v>1.427808304060193</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-2.217117345169875</v>
+        <v>-2.351877110655856</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.225188684482013</v>
+        <v>-3.068371958290584</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.203955988501306</v>
+        <v>-1.016956510453085</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-1.47444293622533</v>
+        <v>-1.311976158189239</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.121200582710316</v>
+        <v>-3.916869976462102</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-2.598137459118384</v>
+        <v>-2.685949977466372</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.06020146049489483</v>
+        <v>0.1031055380046695</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.644289428176528</v>
+        <v>-1.566446267369393</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.7093894468355728</v>
+        <v>-0.6395338303280766</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3901110095800391</v>
+        <v>-0.2987712521472545</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8991398465082625</v>
+        <v>1.004691555382152</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2701746420338793</v>
+        <v>0.4042405024779683</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.7626276485452408</v>
+        <v>-1.248878176989884</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-3.303892508380876</v>
+        <v>-3.45788607888624</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.523981200123707</v>
+        <v>-1.33962738309458</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>3.271793867575369</v>
+        <v>3.502077615322662</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.111916712828055</v>
+        <v>1.756959492668237</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-2.256792290680323</v>
+        <v>-2.058320058589054</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.097928564769852</v>
+        <v>-1.002312587898601</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.9430449615518981</v>
+        <v>-1.152738402529394</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.69292330620641</v>
+        <v>-0.8763588801379782</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.6375754705106615</v>
+        <v>0.5059823068065086</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.124758086503419</v>
+        <v>-1.272334459666013</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.401906413898814</v>
+        <v>-1.530254976065173</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2644248684583275</v>
+        <v>-0.03504180999112805</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-2.219374576487169</v>
+        <v>-1.994308214691742</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.2072240213162218</v>
+        <v>0.4714259242274892</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-5.080078635653969</v>
+        <v>-5.075530920864047</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.810406697466888</v>
+        <v>-4.808655766443884</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-4.011007433828397</v>
+        <v>-4.02141288240805</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.539461025885402</v>
+        <v>-1.865601261627816</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.9029675558539552</v>
+        <v>-1.079109357172207</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-2.999079732307621</v>
+        <v>-3.125542251757196</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-5.815960907496027</v>
+        <v>-5.576516154787711</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-4.536017658211634</v>
+        <v>-4.291262031727292</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-4.717961964936379</v>
+        <v>-4.451590275321109</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-4.58709265339791</v>
+        <v>-4.326694327695058</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.888284970841205</v>
+        <v>-4.603836628139369</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.972865354355996</v>
+        <v>-5.003274054051644</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.726995475941543</v>
+        <v>-1.767933459669045</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.596492615342939</v>
+        <v>2.230617202031759</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.559862405090264</v>
+        <v>3.233947792557892</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.97852893020098</v>
+        <v>2.409115007631009</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.8178868551895775</v>
+        <v>0.8152651117348597</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.288994899655599</v>
+        <v>3.34529523637007</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.725415653199633</v>
+        <v>2.324103350870196</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.4918756625337366</v>
+        <v>0.1059035263340462</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.4552624747825362</v>
+        <v>0.07079367840670869</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.8241252690382765</v>
+        <v>0.4660408095471311</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.02576108551032519</v>
+        <v>-0.3608069532296554</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6316067217467349</v>
+        <v>0.2962692195592922</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.959088322377866</v>
+        <v>1.649968509677755</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.478303910245842</v>
+        <v>-1.773938870246738</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.683602742777929</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="20">
@@ -1300,49 +1300,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.791234553902278</v>
+        <v>1.221823774581111</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.852540813215619</v>
+        <v>-3.309039998203069</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-2.237795029498059</v>
+        <v>-2.717176803280637</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.106804109331136</v>
+        <v>-2.09819459284595</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-4.15528527338337</v>
+        <v>-4.080802418002165</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-1.840918977679266</v>
+        <v>-0.8357389692805768</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.386975163929108</v>
+        <v>3.071786214285908</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.4260259041179</v>
+        <v>3.104981783400582</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.868290973523244</v>
+        <v>3.558424239334613</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.5046882885754513</v>
+        <v>0.2633649361053259</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3007115632653594</v>
+        <v>1.051395457367647</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>1.850241230772198</v>
+        <v>2.599252650619718</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.430090377458789</v>
+        <v>1.706927068309142</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.1406745125338063</v>
+        <v>0.4634346168917247</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-3.464434756935006</v>
+        <v>-2.509116170624935</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.752043382696563</v>
+        <v>-1.079921499690585</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-3.356111153609234</v>
+        <v>-2.678382150014293</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.4364815037065881</v>
+        <v>0.4600364556679679</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-3.145480632711738</v>
+        <v>-3.049436294967727</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.3988664038684604</v>
+        <v>-0.9636912056326352</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-1.099717741298278</v>
+        <v>-1.0255240498132</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.599877336772991</v>
+        <v>-0.2859335600629649</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.890541849969196</v>
+        <v>-2.734458722439911</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6470732290397194</v>
+        <v>-0.5493151601448929</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-1.996652319464367</v>
+        <v>-2.574767535810771</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-1.352518069548111</v>
+        <v>-1.914792714046065</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.5531567277394913</v>
+        <v>-0.1383917919350992</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2823350200480164</v>
+        <v>0.716713676140813</v>
       </c>
     </row>
     <row r="22">
@@ -1404,569 +1404,569 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.214736143378694</v>
+        <v>6.065447142083315</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>11.1252891807496</v>
+        <v>10.91284810949958</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.310227940922147</v>
+        <v>1.224413264379287</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-2.907373002446022</v>
+        <v>-2.227748000566635</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.5471118309040648</v>
+        <v>-0.1580939507788628</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-4.597563888225423</v>
+        <v>-4.187853205608874</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-4.682274247491634</v>
+        <v>-4.961754454278207</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-2.250792166640643</v>
+        <v>-1.842902363853483</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.311774323163419</v>
+        <v>-1.886220272661539</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.712417757174492</v>
+        <v>-1.271750580938914</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.4678435531158343</v>
+        <v>-0.04440514105183979</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>1.74044764271779</v>
+        <v>2.166511065956399</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.578253935233391</v>
+        <v>-1.825769162765702</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.6278806038474301</v>
+        <v>-0.8572998403186816</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 1.275</t>
+          <t>X ≈ 1.274</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>5.926163615483347</v>
+        <v>5.494538205856948</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7751545135699587</v>
+        <v>0.3964566833164369</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.035250385452088</v>
+        <v>3.555732888483973</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5106082724033385</v>
+        <v>1.01721624080443</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.8572744715199789</v>
+        <v>0.5245931384001281</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.500218755482095</v>
+        <v>-0.9818437651648964</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-4.239796371385495</v>
+        <v>-3.701211603608613</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.051997758535002</v>
+        <v>-1.501584691868693</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.422714428332171</v>
+        <v>-6.875381077793776</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.07794295917526</v>
+        <v>-1.476973730722577</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.16759986964783</v>
+        <v>-2.580819823094814</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.24826596508013</v>
+        <v>-1.642584514721968</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.783461066181147</v>
+        <v>-1.144885298428598</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2121860884701192</v>
+        <v>0.8898738493011038</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 1.319</t>
+          <t>X ≈ 1.318</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.064538514920187</v>
+        <v>2.443790265750636</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.862443330947279</v>
+        <v>4.146712388489739</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-1.077782599262378</v>
+        <v>-1.768224145468245</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.870624362507868</v>
+        <v>4.533250225193484</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.332334809412174</v>
+        <v>5.142875378388545</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.356981566319995</v>
+        <v>2.101963386444403</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.408634843417524</v>
+        <v>3.156036603379341</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.941566199630785</v>
+        <v>2.688984226687232</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.607856770380728</v>
+        <v>0.4384080172429918</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.894301610414509</v>
+        <v>0.7244380336241321</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.098691361245166</v>
+        <v>3.839225485931053</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.996705877236785</v>
+        <v>2.78201865988126</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.71291866028708</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.938654310513613</v>
+        <v>3.74701670644378</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 1.363</t>
+          <t>X ≈ 1.362</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>95</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-8.27038971474488</v>
+        <v>-8.802869429845998</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>5.284899451394473</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>5.513126491646844</v>
+        <v>5.929304151315748</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.432825319445698</v>
+        <v>0.8319596224686876</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-4.368622128386868</v>
+        <v>-4.885592062923827</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-6.176511256646521</v>
+        <v>-5.660615001750692</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.103326879070579</v>
+        <v>-2.589659436206269</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.4125007860152792</v>
+        <v>0.08578522759026441</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.684009258327464</v>
+        <v>-4.134903391477835</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-4.481296475710053</v>
+        <v>-4.325104801124645</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-2.580734476075442</v>
+        <v>-2.456607967669342</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.704251060562136</v>
+        <v>-5.580554439533891</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.019138755980869</v>
+        <v>-3.870449208203041</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.4171232100352285</v>
+        <v>0.5891219696018908</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 1.407</t>
+          <t>X ≈ 1.406</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>7.896442460031686</v>
+        <v>10.18372387932936</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.6248790084772367</v>
+        <v>-1.115496485883604</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-3.543477281938124</v>
+        <v>-3.444387620424223</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.247125220140745</v>
+        <v>4.47554054301461</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.951541691445406</v>
+        <v>-1.857614787864293</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1194172438500019</v>
+        <v>0.3668010562873576</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.03470688458383364</v>
+        <v>0.3152989554547148</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.319154212033034</v>
+        <v>-4.053794455594137</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>7.053825895595075</v>
+        <v>7.59887611280147</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>9.977492004925651</v>
+        <v>10.69112376640179</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>7.885998393835266</v>
+        <v>6.5861648221344</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>9.807168999020725</v>
+        <v>8.599012123933541</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>3.726640787216752</v>
+        <v>2.321501256193251</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.839168890273413</v>
+        <v>4.531330431934045</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 1.451</t>
+          <t>X ≈ 1.45</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.074639525021205</v>
+        <v>1.666459017865442</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-5.203213234709224</v>
+        <v>-2.138002424675115</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-3.375762397242113</v>
+        <v>-4.696429478456039</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-3.245537253653751</v>
+        <v>-4.53824779128211</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-6.006049028971724</v>
+        <v>-9.283301183672329</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-5.70867499933658</v>
+        <v>-4.777349530182541</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-5.793385358602677</v>
+        <v>-4.866303265367314</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-1.816009557945108</v>
+        <v>1.037421528427231</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-6.321436158912192</v>
+        <v>-5.329491930544428</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.726910510797673</v>
+        <v>-1.965430610223251</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.709389446835587</v>
+        <v>1.310729777894664</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>1.339938281630673</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.095162147793729</v>
+        <v>0.9447803550668468</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.869426497567197</v>
+        <v>1.193825217082214</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 1.495</t>
+          <t>X ≈ 1.494</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>30</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-5.814249363867688</v>
+        <v>-5.813525397578466</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-4.045689290839881</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.105413951261184</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2.310018301901806</v>
+        <v>2.334683608245477</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>5.105062082139547</v>
+        <v>5.172647849586518</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5.402436111774442</v>
+        <v>5.443733382005263</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>5.317725752508274</v>
+        <v>5.391577224780427</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>4.850657108721627</v>
+        <v>4.91724453239646</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5.210325047801341</v>
+        <v>-5.079268400417689</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.6064228225356558</v>
+        <v>0.7462298241527847</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>3.735054997608707</v>
+        <v>3.862502813309113</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.436099816630886</v>
+        <v>0.5597964376591307</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.349282296650713</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.2416846135439101</v>
+        <v>0.4136833731105725</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 1.539</t>
+          <t>X ≈ 1.538</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>38</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>8.045399758939332</v>
+        <v>7.983886328390966</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>11.69737156061235</v>
+        <v>11.67771755348445</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.30260017585731</v>
+        <v>11.30244678585299</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>11.43282531944568</v>
+        <v>11.41848041155514</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>18.7892726084552</v>
+        <v>18.79165047651279</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>13.82348874335356</v>
+        <v>13.82667052903444</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>16.37035733145574</v>
+        <v>16.39528498459183</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>15.903288687669</v>
+        <v>15.9179102112816</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>18.47388547851472</v>
+        <v>18.50097453658612</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>17.62396668218477</v>
+        <v>17.68868796869816</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>25.31400236602985</v>
+        <v>25.33773311672999</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>22.71680157101668</v>
+        <v>22.84049819204493</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>17.03349282296649</v>
+        <v>17.18218237074432</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>11.99607057845619</v>
+        <v>12.16806933802285</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 1.583</t>
+          <t>X ≈ 1.582</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>32</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-14.98091603053435</v>
+        <v>-14.91101122528675</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.282897876401819</v>
+        <v>5.295660123934518</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>11.13812649164682</v>
+        <v>11.13901407432739</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>11.26835163523514</v>
+        <v>11.24891143999238</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>4.480062082139405</v>
+        <v>4.552550373657333</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>11.02743611177453</v>
+        <v>11.03911004304256</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>23.44272575250837</v>
+        <v>23.412664480133</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>19.85065710872163</v>
+        <v>19.82495463780413</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>22.91467495219885</v>
+        <v>22.89320354765471</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>18.93975615586899</v>
+        <v>18.98080901081055</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>12.4850549976088</v>
+        <v>12.5562321875249</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>15.64443314996412</v>
+        <v>15.76812977099237</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>18.34928229665071</v>
+        <v>18.49797184442854</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>12.32501794687725</v>
+        <v>12.49701670644391</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 1.627</t>
+          <t>X ≈ 1.626</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>18.35241730279899</v>
+        <v>18.95383974363256</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>16.74123120973516</v>
+        <v>17.12300167884002</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>16.34645982497999</v>
+        <v>16.56415637076741</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>20.64335163523514</v>
+        <v>16.85914773173999</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>15.93839541547279</v>
+        <v>16.28734493090906</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>12.06910277844119</v>
+        <v>12.23982224939779</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.98439241917502</v>
+        <v>12.17916616017233</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>11.51732377538828</v>
+        <v>16.17123103325078</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>3.123008285532187</v>
+        <v>7.466124136827261</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>14.77308948920233</v>
+        <v>15.17284041016741</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.235054997608799</v>
+        <v>10.64839176230112</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>4.762694988383728</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>10.01594896331737</v>
+        <v>8.715363148776369</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>10.2416846135439</v>
+        <v>8.964408010791793</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 1.671</t>
+          <t>X ≈ 1.67</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.22496632240682</v>
+        <v>8.60099928622413</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>16.49613317051947</v>
+        <v>12.57337775662375</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>16.10136178576443</v>
+        <v>12.17963976830904</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.466881046999852</v>
+        <v>6.753968253968168</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.810944435080621</v>
+        <v>6.264719113016334</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>10.10831846471571</v>
+        <v>6.537504631835262</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>10.02360810544954</v>
+        <v>6.476848542609801</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.208166420690134</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-8.151501518389388</v>
+        <v>-10.69262349357709</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.119067373542769</v>
+        <v>-0.405340963280878</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.440937350549973</v>
+        <v>4.946074144738589</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.592962561728832</v>
+        <v>5.004240882103396</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.172811708415423</v>
+        <v>4.609082955539655</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>8.28090029981842</v>
+        <v>10.41368337311049</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>16</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.480916030534353</v>
+        <v>-2.510111824886984</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>20.90789787640186</v>
+        <v>20.90671108995721</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.763126491646865</v>
+        <v>1.762973101642544</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.893351635235142</v>
+        <v>1.892857142857139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-4.894937917860553</v>
+        <v>-4.846391998094781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.597563888225466</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.567725752508366</v>
+        <v>1.615737431498687</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.149342891278373</v>
+        <v>-5.100095328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-11.46032504780115</v>
+        <v>-11.38706793802145</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-12.31024384413101</v>
+        <v>-12.21089651883644</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-6.264945002391201</v>
+        <v>-6.165036966372526</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-12.48056685003588</v>
+        <v>-12.35687022900763</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-12.90071770334929</v>
+        <v>-12.75202815557146</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-12.67498205312275</v>
+        <v>-12.50298329355609</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>16</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-14.98091603053435</v>
+        <v>-15.01011182488698</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-10.34210212359822</v>
+        <v>-10.34328891004288</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.013126491646823</v>
+        <v>8.012973101642501</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.143351635235184</v>
+        <v>8.142857142857181</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>7.605062082139447</v>
+        <v>7.653608001905219</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>7.902436111774534</v>
+        <v>7.926393520724147</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>14.06772575250837</v>
+        <v>14.11573743149869</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>13.60065710872167</v>
+        <v>13.64990467111539</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>19.78967495219885</v>
+        <v>19.86293206197855</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>12.68975615586903</v>
+        <v>12.78910348116361</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>12.48505499760876</v>
+        <v>12.58496303362743</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.269433149964122</v>
+        <v>6.393129770992367</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>12.09928229665071</v>
+        <v>12.24797184442854</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
   </sheetData>
@@ -2210,625 +2210,625 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; 0.5058</t>
+          <t>X &gt; 0.5054</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4101</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0430808281940287</v>
+        <v>-0.0423267531631808</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.06542043187609892</v>
+        <v>0.04095233509334406</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.02345887420687376</v>
+        <v>-0.02339274608315378</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.04686468719903303</v>
+        <v>0.02241918665275477</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.08310014948936839</v>
+        <v>0.05747755654138587</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.0210444837831929</v>
+        <v>-0.04585574899347478</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.0784679400083661</v>
+        <v>0.0528569834831103</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01549227355679506</v>
+        <v>-0.009983297710768113</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.1389665985105211</v>
+        <v>0.1235263142922349</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.08439334130753906</v>
+        <v>0.0683361242817071</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.01560240718847439</v>
+        <v>-0.0003196174446529199</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.01484991848037964</v>
+        <v>-0.00158141594401684</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.02409892256758184</v>
+        <v>0.00699183467719422</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.06804802758157535</v>
+        <v>0.05035735506619687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; 0.5497</t>
+          <t>X &gt; 0.5494</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4023</v>
+        <v>4035</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.09589269097208586</v>
+        <v>0.08504388445557254</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.009508780986706711</v>
+        <v>-0.001817958250505569</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.04959041464970682</v>
+        <v>-0.06071631477692563</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.06933725388130796</v>
+        <v>0.03316137238966377</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.06537954245690969</v>
+        <v>0.02743284109374144</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-0.02053585547924541</v>
+        <v>-0.05739762008258253</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.106807638364451</v>
+        <v>0.0687077285283948</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1000986574930351</v>
+        <v>0.07317199784802142</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07765906342030604</v>
+        <v>0.06095186395874919</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.08577055865022487</v>
+        <v>0.09258206497143817</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.03046909578414869</v>
+        <v>-0.02338268207336824</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.03180908606071853</v>
+        <v>-0.02562177718697001</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.009322058082126716</v>
+        <v>0.01432466900732976</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.07514223223643057</v>
+        <v>0.07911088240425102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; 0.5937</t>
+          <t>X &gt; 0.5933</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3943</v>
+        <v>3953</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1360245510079992</v>
+        <v>0.1387277311170507</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.1061780989612515</v>
+        <v>0.1080736940449754</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.1230991597572171</v>
+        <v>-0.1205453233953975</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.223311149405184</v>
+        <v>0.1997872110217358</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.179726724002272</v>
+        <v>0.1536080019052264</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.08598041557200276</v>
+        <v>0.06140236134046262</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.2683461627388013</v>
+        <v>0.241937532559831</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2457938868371343</v>
+        <v>0.2308799111355526</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1481750788773439</v>
+        <v>0.1433767310033147</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.04720673873771375</v>
+        <v>0.04112521480016085</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.04187782875368384</v>
+        <v>-0.04774677425928076</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.05819676131597618</v>
+        <v>-0.05124443886857222</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.007715674951718654</v>
+        <v>-0.002281064018603729</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1309398337654031</v>
+        <v>0.1345704630844367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; 0.6376</t>
+          <t>X &gt; 0.6373</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3846</v>
+        <v>3856</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3321511201008533</v>
+        <v>0.3474004585368604</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1350762996383281</v>
+        <v>0.1488217987000482</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.06404601159576373</v>
+        <v>-0.04976945980644132</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2996421670120526</v>
+        <v>0.2753623188405783</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.2166344744591129</v>
+        <v>0.1885549343411554</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.1909126235835146</v>
+        <v>0.1907643130597307</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.3021494285208277</v>
+        <v>0.2737923395535944</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.4466062128504191</v>
+        <v>0.4295602007708723</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.2442204067443043</v>
+        <v>0.263087462133953</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.136170809025657</v>
+        <v>0.1271863827179658</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.10590134334754</v>
+        <v>-0.114246606175584</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.04553566500469231</v>
+        <v>-0.04155141096720172</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.0688040018755629</v>
+        <v>0.07043749130435373</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.1012789973192625</v>
+        <v>0.1526183661949432</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; 0.6816</t>
+          <t>X &gt; 0.6812</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3752</v>
+        <v>3760</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.3633157610658628</v>
+        <v>0.3546096605241544</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.04243656292135967</v>
+        <v>0.04464212443991755</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.2315543594170535</v>
+        <v>-0.228602913215596</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.111436741618121</v>
+        <v>0.1014558689717902</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.07846633745859322</v>
+        <v>0.07795098040269721</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.01802536423529233</v>
+        <v>0.02012692486647438</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.1873372479846864</v>
+        <v>0.1864545629727914</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.1873619263953046</v>
+        <v>0.1987094519918386</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.007992311091292947</v>
+        <v>0.02893471802104841</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.02828645398454199</v>
+        <v>-0.009780684617524571</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.2180616779372926</v>
+        <v>-0.1990523796066412</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.1304070205206926</v>
+        <v>-0.09942737945951308</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.0772332692059976</v>
+        <v>0.1052571408922489</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1581735971970701</v>
+        <v>0.2097826638907136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; 0.7256</t>
+          <t>X &gt; 0.7252</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3618</v>
+        <v>3628</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2754235505020333</v>
+        <v>0.2661388623037766</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02976167568497345</v>
+        <v>0.02985567489393759</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.2397692612489735</v>
+        <v>-0.2390202995123403</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1110846743967571</v>
+        <v>0.09830268741159642</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1243671014444701</v>
+        <v>0.0917097900757895</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.02312576694694712</v>
+        <v>-0.005637299308872912</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.09145643683508098</v>
+        <v>0.05882854077476907</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.1639333990887266</v>
+        <v>0.143505001420877</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1578678418375929</v>
+        <v>-0.1687222182306485</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1640825627170415</v>
+        <v>-0.1789581928452506</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.2428455548773911</v>
+        <v>-0.2575734576972337</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.09797016495301136</v>
+        <v>-0.1013605871343586</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.07766030162446214</v>
+        <v>0.07003026272559509</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.07031921829791798</v>
+        <v>0.08659774282758548</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; 0.7695</t>
+          <t>X &gt; 0.7691</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3457</v>
+        <v>3465</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.07110362072194931</v>
+        <v>-0.1072341270452526</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2526102067390497</v>
+        <v>-0.2803392697550677</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3141908632478234</v>
+        <v>-0.2843786542585249</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.1336779419056668</v>
+        <v>0.1490477561597601</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.08629222941060277</v>
+        <v>0.1075250525964648</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.1395822700645439</v>
+        <v>0.1656617431384433</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.0417939408932213</v>
+        <v>0.06314377155632656</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.09153942307028728</v>
+        <v>-0.05686766317860759</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.3100648569945577</v>
+        <v>-0.266750935139612</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.3054722998857784</v>
+        <v>-0.2676131518718918</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.394499658261644</v>
+        <v>-0.3403541520703328</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.2733661559930809</v>
+        <v>-0.2372423086153574</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.2434281459295633</v>
+        <v>-0.1835053627266774</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1044729411759846</v>
+        <v>-0.004787045359847752</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; 0.8135</t>
+          <t>X &gt; 0.8131</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3246</v>
+        <v>3253</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.05313483815574216</v>
+        <v>-0.07370361158633898</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.3263474356178548</v>
+        <v>-0.3390749964663726</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.3355819954380834</v>
+        <v>-0.317805561754227</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1021462231810233</v>
+        <v>0.1046786699960478</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.08661189763760291</v>
+        <v>0.09225830865369034</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.09330046120548019</v>
+        <v>0.07505875545873408</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.0668896321070207</v>
+        <v>-0.06090468022629381</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.03686825061143395</v>
+        <v>0.05644242433817936</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.3765812054366151</v>
+        <v>-0.3488543100288197</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.1932897326434784</v>
+        <v>-0.1733619778477973</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.4287885502815598</v>
+        <v>-0.391081192416749</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.2096244416589172</v>
+        <v>-0.1928917343839842</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1812167791348642</v>
+        <v>-0.1713582108879947</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.01709542342466364</v>
+        <v>0.03352147127636584</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; 0.8574</t>
+          <t>X &gt; 0.857</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2978</v>
+        <v>2989</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.08560614778728848</v>
+        <v>-0.1259837822060987</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3052388528206933</v>
+        <v>-0.3753829413866185</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4137927172033713</v>
+        <v>-0.451002882346863</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.05166541331090713</v>
+        <v>0.03057819724485711</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.2508884314522248</v>
+        <v>0.1936614064446118</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.03686636978146396</v>
+        <v>-0.08278844922577377</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.06972812203037648</v>
+        <v>-0.1252445324291713</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1191134845605504</v>
+        <v>0.1103255127987168</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.3261357225242136</v>
+        <v>-0.3608488331450275</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.08307796098795706</v>
+        <v>-0.09721459434594948</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3213587028613105</v>
+        <v>-0.3495289449821541</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.08550304882701454</v>
+        <v>-0.07209924940215018</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.0691193151692957</v>
+        <v>-0.0471786572436983</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.04486116662175021</v>
+        <v>0.0200177101240655</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.9014</t>
+          <t>X &gt; 0.901</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2677</v>
+        <v>2683</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.4821849758018359</v>
+        <v>0.4791195156254631</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2703139837843693</v>
+        <v>0.2698748478479942</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.06688096825623546</v>
+        <v>-0.1036688002891921</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.1752427206510276</v>
+        <v>0.1207464033550991</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3083444394687973</v>
+        <v>0.2465448048791998</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.00892622740302329</v>
+        <v>-0.01800960311371114</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2792891728647717</v>
+        <v>-0.3187863780251234</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.352777008486278</v>
+        <v>-0.3753929479322693</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3559561157623179</v>
+        <v>-0.3751631761166863</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.06472647394050313</v>
+        <v>-0.09934088057816126</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.007940893313879371</v>
+        <v>-0.02207345185279763</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.01091798937095234</v>
+        <v>-0.01748475414730422</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.2442926006223587</v>
+        <v>-0.2427136995356918</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2053331924578288</v>
+        <v>-0.159058582411852</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.9453</t>
+          <t>X &gt; 0.9449</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2353</v>
+        <v>2359</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.8891560338997309</v>
+        <v>0.8682665534913951</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.7425034743662025</v>
+        <v>0.7631300088760753</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.01084465811987201</v>
+        <v>-0.01067554700619411</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.4163681816925049</v>
+        <v>0.4379564246484335</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4296272072985445</v>
+        <v>0.4367863620066572</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.07910822424582875</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.2680127873897717</v>
+        <v>-0.2349393874522505</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2024214475416457</v>
+        <v>-0.1931579346376182</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1975807827204363</v>
+        <v>-0.1455281749080939</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1658505035102991</v>
+        <v>0.1965304807403712</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2586419079360383</v>
+        <v>0.3125244222811574</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.3780179353444879</v>
+        <v>0.4369671280444649</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2128607071904511</v>
+        <v>0.2776328613776968</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3535984823638572</v>
+        <v>0.4659654135231861</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.9893</t>
+          <t>X &gt; 0.9889</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2002</v>
+        <v>2006</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8823126690172174</v>
+        <v>0.8893918971973775</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.6436904985354133</v>
+        <v>0.6461651842499663</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3759693844148657</v>
+        <v>0.4013105706250855</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.054822956930899</v>
+        <v>1.054972336501621</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7160346507180009</v>
+        <v>0.6926045245082975</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.1655283811012183</v>
+        <v>0.1977652901078528</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.4075461117898058</v>
+        <v>0.4129776105140976</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.2176066843581737</v>
+        <v>0.2455038754912735</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.2427763708166282</v>
+        <v>-0.1892807674595431</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.4832126993255272</v>
+        <v>0.5067651727058546</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.4283616909154873</v>
+        <v>0.4800600968430047</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.5126898932208661</v>
+        <v>0.5664365439007355</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.09253903990745727</v>
+        <v>0.1496908279860918</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3682247400840453</v>
+        <v>0.4768272747390228</v>
       </c>
     </row>
     <row r="18">
@@ -2838,49 +2838,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1681</v>
+        <v>1689</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.196426792715947</v>
+        <v>1.290713160381138</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.397512119725256</v>
+        <v>1.416434130617148</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.7387796982976056</v>
+        <v>0.7280585465452276</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.631475150674575</v>
+        <v>0.5956873315363822</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.4494801343959764</v>
+        <v>0.4928410402532961</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.62808931842536</v>
+        <v>0.6211987155293457</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6950281886343319</v>
+        <v>0.6786063807312743</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.4392421265575379</v>
+        <v>0.5079330064164083</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.156817318906981</v>
+        <v>-0.06032649764364351</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.453735929813071</v>
+        <v>0.5069121049083947</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.724941969649251</v>
+        <v>0.8089583054950893</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.8782969215286656</v>
+        <v>0.9599541352738541</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1607040694050283</v>
+        <v>0.1843623769729277</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.8623469177279262</v>
+        <v>0.9406223902804953</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1383</v>
+        <v>1388</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.409573883010317</v>
+        <v>1.468382798768928</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>2.793261971571255</v>
+        <v>2.824273813971502</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.934482913003194</v>
+        <v>1.928743710961456</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.631807623691131</v>
+        <v>1.59694609551137</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.093518070595437</v>
+        <v>1.004289983240469</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.9579916673300914</v>
+        <v>0.9899254661656371</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>1.491010951064325</v>
+        <v>1.503569448727696</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>1.787073293692721</v>
+        <v>1.827399287052167</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.7867847787884514</v>
+        <v>0.8571890612606694</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>1.568100335189314</v>
+        <v>1.58220692943943</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.86954523622051</v>
+        <v>1.922669719464999</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>2.120843128272142</v>
+        <v>2.166511065956399</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.266852795566116</v>
+        <v>1.309346934421342</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.420281865893877</v>
+        <v>1.527996533533248</v>
       </c>
     </row>
     <row r="20">
@@ -2942,49 +2942,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.3718978222795</v>
+        <v>1.316199439085501</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.840306888533533</v>
+        <v>2.742480651436097</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.925604827868618</v>
+        <v>1.832835526406001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.795864633502042</v>
+        <v>1.753012048192765</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6509892918448159</v>
+        <v>0.536898268916417</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.6017428708733235</v>
+        <v>0.7235511434631618</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>1.692400514000127</v>
+        <v>1.782619429776034</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>2.055518219832742</v>
+        <v>2.178113112114481</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.7792582855321868</v>
+        <v>0.9352834831671757</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.889365191490185</v>
+        <v>1.970137963922191</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>2.119068898564485</v>
+        <v>2.247387537510129</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>2.153447050919809</v>
+        <v>2.26964099724453</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.820177170673304</v>
+        <v>1.92493813656337</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.045912820899837</v>
+        <v>2.173982998578737</v>
       </c>
     </row>
     <row r="21">
@@ -2994,49 +2994,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>953</v>
+        <v>956</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.284774346034688</v>
+        <v>1.336042021266863</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>4.023081122475119</v>
+        <v>4.014819198065268</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>2.790613402641547</v>
+        <v>2.789480378149733</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2.606702420575459</v>
+        <v>2.562732272929978</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.649564699940498</v>
+        <v>1.507774668571891</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.109242394497045</v>
+        <v>1.051393520724147</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>1.548092244654967</v>
+        <v>1.511570764832015</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.978539708302343</v>
+        <v>1.983238004448673</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3452305077544082</v>
+        <v>0.383765395311876</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>2.386765599730481</v>
+        <v>2.328988778348126</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.496859824471336</v>
+        <v>2.498846123397826</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>2.216442593825612</v>
+        <v>2.200339802340331</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.901223534845883</v>
+        <v>1.970775191708874</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>2.44175456807347</v>
+        <v>2.533627585104988</v>
       </c>
     </row>
     <row r="22">
@@ -3046,49 +3046,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.271935680492263</v>
+        <v>2.138129381143159</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>5.22348723001398</v>
+        <v>5.077565361313951</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>4.068259571494693</v>
+        <v>3.930058528778133</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.057800304436668</v>
+        <v>3.001347708894876</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.646253463635006</v>
+        <v>2.458393896111765</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.422714945741589</v>
+        <v>1.471733571101979</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>2.098460860239669</v>
+        <v>2.040800403790875</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>2.265105777923154</v>
+        <v>2.45657973408764</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.8099537861659059</v>
+        <v>1.034216696739257</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>2.748374660304989</v>
+        <v>2.92939351899458</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>3.430872488103098</v>
+        <v>3.557185255849696</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.958279791282251</v>
+        <v>3.058742918906397</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>2.411386225674789</v>
+        <v>2.410740491710463</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>2.890607300489407</v>
+        <v>2.912629854357938</v>
       </c>
     </row>
     <row r="23">
@@ -3098,517 +3098,517 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.436134660709889</v>
+        <v>1.300863784869115</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.972414005434082</v>
+        <v>3.833540358249842</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>4.65291143788334</v>
+        <v>4.506875540666854</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4.32230708838415</v>
+        <v>4.116139585605225</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.32318804220089</v>
+        <v>3.01620342175255</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.698903085660859</v>
+        <v>2.678301917670709</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.535851712569809</v>
+        <v>3.533676362796399</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.222392899812256</v>
+        <v>3.37318711386343</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.471702601968438</v>
+        <v>1.65682519174954</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.693980426222296</v>
+        <v>3.825036202876106</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.257328423108028</v>
+        <v>4.325008975434521</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>3.216437758259055</v>
+        <v>3.248957991851263</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>3.257116398033197</v>
+        <v>3.31392276467394</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.636461879288916</v>
+        <v>3.716341859818137</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 1.297</t>
+          <t>X &gt; 1.296</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4930616646329327</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.64395735595572</v>
+        <v>4.546416972310105</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>4.992680394992504</v>
+        <v>4.704149572230698</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5.122905538580866</v>
+        <v>4.758879242304658</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.841121561693349</v>
+        <v>3.53298185089232</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.580874773484574</v>
+        <v>3.437443244481052</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.169026867750006</v>
+        <v>5.03424571879151</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4.330211012067352</v>
+        <v>4.384250895793066</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.339860825804806</v>
+        <v>3.426467973580749</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.906298906798355</v>
+        <v>4.924712337252124</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.816839384225901</v>
+        <v>5.757329022536894</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>4.364228688997578</v>
+        <v>4.263500141362741</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>4.315825047580077</v>
+        <v>4.238712585169282</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>4.355687091858663</v>
+        <v>4.302572261999458</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 1.341</t>
+          <t>X &gt; 1.34</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>450</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.1857506361323118</v>
+        <v>0.02851952169138627</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.796786765290712</v>
+        <v>4.626357889074164</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>6.179793158313451</v>
+        <v>5.998624315770492</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.976684968568478</v>
+        <v>4.804005045726896</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.54950652658389</v>
+        <v>3.211003145393072</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.624658333996756</v>
+        <v>3.704539216088385</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>5.317725752508366</v>
+        <v>5.409887541873957</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.406212664277177</v>
+        <v>4.723304229614236</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.678563841087744</v>
+        <v>4.024079964848305</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>5.495311711424542</v>
+        <v>5.764767197977726</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>5.95727721983102</v>
+        <v>6.140949729858072</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.436099816630794</v>
+        <v>4.559796437659038</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>4.238171185539606</v>
+        <v>4.386860733317434</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.241684613543917</v>
+        <v>4.41368337311058</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 1.385</t>
+          <t>X &gt; 1.384</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>355</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.448661434254383</v>
+        <v>2.391848959426746</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.499447172176467</v>
+        <v>4.450128456903947</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>6.358196914181988</v>
+        <v>6.017174782314726</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5.925041776080207</v>
+        <v>5.86694677871148</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>5.668442363829584</v>
+        <v>5.37769763775956</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>6.247506534309743</v>
+        <v>6.210707246214341</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>7.571246879268926</v>
+        <v>7.550611381078518</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>5.695727531256836</v>
+        <v>5.964330441423471</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.916435515579131</v>
+        <v>6.2074698771046</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>8.165108268545055</v>
+        <v>8.464873789286813</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>8.242097251129934</v>
+        <v>8.44170460666119</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.14971484010497</v>
+        <v>7.273411461133215</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>6.447873845946489</v>
+        <v>6.596563393724317</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>5.265158791947663</v>
+        <v>5.437157551514325</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 1.429</t>
+          <t>X &gt; 1.428</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.492593903240483</v>
+        <v>1.084659416943083</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>5.179421055209772</v>
+        <v>5.383835272963701</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>8.09590794860042</v>
+        <v>7.604476369616314</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6.570503953115939</v>
+        <v>6.100373482726418</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>7.356717711278513</v>
+        <v>6.591516498637247</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>7.32296591309904</v>
+        <v>7.191099403077089</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>8.893884692905722</v>
+        <v>8.764430241956198</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>7.102312737860693</v>
+        <v>7.645002710331028</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>5.716827270079648</v>
+        <v>5.974043173089662</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>7.847040924080915</v>
+        <v>8.091391062862911</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8.304591421449857</v>
+        <v>8.752995820512723</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>6.683340434732337</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>6.925441237048069</v>
+        <v>7.313761318112753</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>5.164421920387184</v>
+        <v>5.589121969601806</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 1.473</t>
+          <t>X &gt; 1.472</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>257</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.215582023940357</v>
+        <v>0.9782602681362675</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>6.997392039825947</v>
+        <v>6.759424268251735</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>10.10456618036273</v>
+        <v>9.854058372960296</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8.289266032122299</v>
+        <v>8.045957918050938</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>9.696501770855399</v>
+        <v>9.494693273223056</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>9.604770742124728</v>
+        <v>9.379881892817174</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11.46558567468735</v>
+        <v>11.25721029971574</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>8.663886680706057</v>
+        <v>8.853393043208371</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>7.824694407451766</v>
+        <v>8.04122663562196</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>9.698511019682215</v>
+        <v>9.930576349380615</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>9.88291491978778</v>
+        <v>10.11403280106933</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>7.971767780314316</v>
+        <v>8.095464401342561</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>8.329827043732422</v>
+        <v>8.47851659151025</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>6.220932343764403</v>
+        <v>6.392931103331065</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 1.517</t>
+          <t>X &gt; 1.516</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>227</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.144634630258601</v>
+        <v>1.875853087393722</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>8.462963955696971</v>
+        <v>8.187412844343136</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>11.5924216458318</v>
+        <v>11.30244678585299</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>9.079474983252766</v>
+        <v>8.800751879699241</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>10.30329996760199</v>
+        <v>10.0658887036596</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>10.16014536287587</v>
+        <v>9.900077731250462</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>12.27807817541586</v>
+        <v>12.03240409816534</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>9.167837725461716</v>
+        <v>9.373588881641659</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.547384203300183</v>
+        <v>9.775212763732931</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>10.90010857877648</v>
+        <v>11.1443666390583</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>10.69540742051629</v>
+        <v>10.94022619152221</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>8.967671035426669</v>
+        <v>9.091367656454914</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>8.988048816474503</v>
+        <v>9.136738364252331</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>7.01114129489487</v>
+        <v>7.183140054461532</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 1.561</t>
+          <t>X &gt; 1.56</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>189</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.958237408619091</v>
+        <v>0.6477829119551188</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>7.812659781163724</v>
+        <v>7.485658458378218</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>11.65069262921292</v>
+        <v>11.30244678585299</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8.606314598198104</v>
+        <v>8.274436090225556</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>8.597125574202934</v>
+        <v>8.311502738747322</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>9.42360013293856</v>
+        <v>9.110604047039935</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>11.45529189007451</v>
+        <v>11.15521111570922</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>7.813620071684589</v>
+        <v>8.057799407957447</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7.752637915161813</v>
+        <v>8.02082679882065</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9.548221764334599</v>
+        <v>9.828577165374099</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>7.756219018772825</v>
+        <v>8.045489349416954</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>6.203295583826552</v>
+        <v>6.326992204854797</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>7.370446317814739</v>
+        <v>7.519135865592567</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>6.008880380739676</v>
+        <v>6.180879140306338</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 1.605</t>
+          <t>X &gt; 1.604</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>157</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>4.206982058637621</v>
+        <v>3.819002099163647</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>8.328280042006909</v>
+        <v>7.932027545653362</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>11.75516470820728</v>
+        <v>11.33575791176904</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>8.063733800840232</v>
+        <v>7.668173598553338</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>9.436272273222251</v>
+        <v>9.077658634816608</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>9.096703627698098</v>
+        <v>8.71753276123048</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>9.011993268431929</v>
+        <v>8.656876672005019</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.360211248849012</v>
+        <v>5.659398342001424</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>4.662286417167003</v>
+        <v>4.989514340459557</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>7.634023671792555</v>
+        <v>7.963154114074953</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>6.79237983837313</v>
+        <v>7.126102274133807</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.278987290091507</v>
+        <v>4.402683911119752</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>5.132721787096571</v>
+        <v>5.281411334874399</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>4.721514762163871</v>
+        <v>4.893513521730533</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 1.649</t>
+          <t>X &gt; 1.648</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.654422315330308</v>
+        <v>1.221231458695108</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>6.810153515499564</v>
+        <v>6.354472283987008</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.92666032623325</v>
+        <v>10.43834623597081</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5.793727575084766</v>
+        <v>6.090618336886983</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>8.26295681898155</v>
+        <v>7.840175166084329</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>8.560330848616637</v>
+        <v>8.112960684903257</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>8.475620489350469</v>
+        <v>8.052304595677796</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.24915334932313</v>
+        <v>3.855128551712362</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>4.940050892048475</v>
+        <v>4.564424599291975</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>6.34577119346298</v>
+        <v>6.725670645342674</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>6.892949734450902</v>
+        <v>6.521530197806584</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.919809089813747</v>
+        <v>4.340890965022211</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>4.251537935748459</v>
+        <v>4.69200169517481</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3.72539388672687</v>
+        <v>4.194777900473753</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>116</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.1052908660173699</v>
+        <v>0.07609507166473861</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>5.390656497091477</v>
+        <v>5.389469710646821</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>10.16829890543989</v>
+        <v>10.16814551543557</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5.988179221442039</v>
+        <v>5.987684729064036</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.036096564898067</v>
+        <v>8.084642484663839</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>8.333470594533154</v>
+        <v>8.357428003482767</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>8.248760235266985</v>
+        <v>8.296771914257306</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.195484694928524</v>
+        <v>5.244732257322241</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>6.858640469440232</v>
+        <v>6.931897579219928</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>7.732859604144856</v>
+        <v>7.83220692943943</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>6.666089480367418</v>
+        <v>6.765997516386093</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>4.114260736171019</v>
+        <v>4.237957357199264</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>4.556178848374849</v>
+        <v>4.704868396152676</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.057776567566904</v>
+        <v>3.229775327133567</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>100</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.5190839694656475</v>
+        <v>0.4898881751130162</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>2.907897876401812</v>
+        <v>2.906711089957156</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>11.51312649164678</v>
+        <v>11.51297310164246</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6.643351635235142</v>
+        <v>6.642857142857139</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>10.10506208213945</v>
+        <v>10.15360800190522</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.40243611177453</v>
+        <v>10.42639352072415</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>9.317725752508366</v>
+        <v>9.365737431498687</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>6.850657108721627</v>
+        <v>6.899904671115344</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.789674952198851</v>
+        <v>9.862932061978547</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>10.93975615586899</v>
+        <v>11.03910348116356</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.735054997608799</v>
+        <v>8.834963033627474</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>6.769433149964122</v>
+        <v>6.893129770992367</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.349282296650713</v>
+        <v>7.497971844428541</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>5.575017946877246</v>
+        <v>5.747016706443908</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.471464921846604</v>
+        <v>3.442269127493972</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>5.431707400211344</v>
+        <v>5.430520613766689</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>12.17979315831344</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.357142857142847</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>10.58125255832993</v>
+        <v>10.6297984780957</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>10.87862658796502</v>
+        <v>10.90258399691463</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>8.412963847746461</v>
+        <v>8.460975526736782</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>5.564942823007335</v>
+        <v>5.614190385401052</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>7.884913047436946</v>
+        <v>7.958170157216642</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>10.60642282253565</v>
+        <v>10.70577014783022</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>8.020769283323091</v>
+        <v>8.120677319341766</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>6.864671245202217</v>
+        <v>6.988367866230462</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>6.444520391888808</v>
+        <v>6.593209939666636</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>6.670256042115341</v>
+        <v>6.842254801682003</v>
       </c>
     </row>
   </sheetData>
@@ -3904,625 +3904,625 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; 0.5058</t>
+          <t>X &lt; 0.5054</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.090512540894217</v>
+        <v>1.061316746541586</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-1.711149742645794</v>
+        <v>-0.5218603386142675</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.975695983812471</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-3.704461727384363</v>
+        <v>-2.465439617142394</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.545293254631673</v>
+        <v>3.759726854057483</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-1.110845676063065</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>1.993514251578766</v>
+        <v>3.23323800444868</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-2.829372666848762</v>
+        <v>-2.125019745250363</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.1078628917500524</v>
+        <v>0.6656095052599582</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>3.258864521418325</v>
+        <v>4.075926889049164</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>3.293242673773648</v>
+        <v>4.134093626414057</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>2.873091820460239</v>
+        <v>3.738935699850231</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>1.578342007648722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; 0.5497</t>
+          <t>X &lt; 0.5494</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.147582697201017</v>
+        <v>-2.841237652701558</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.5745645430684831</v>
+        <v>0.8735985071757071</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.8464598249801156</v>
+        <v>1.142112174490137</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-1.689981698098194</v>
+        <v>-0.7147587511826003</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-1.561604584527217</v>
+        <v>-0.5417562365053783</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.402436111774541</v>
+        <v>2.380035904830109</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-0.3296268069119108</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.149342891278373</v>
+        <v>-0.4334286622179917</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1230082855321868</v>
+        <v>0.5676300485557277</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.06024384413100137</v>
+        <v>-0.2561985322592548</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>3.068388330942135</v>
+        <v>2.895365718191236</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>3.102766483297458</v>
+        <v>2.953532455556129</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>2.015948963317378</v>
+        <v>1.887233589394988</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.2416846135439101</v>
+        <v>0.1228556326184034</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; 0.5937</t>
+          <t>X &lt; 0.5933</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.697366246984565</v>
+        <v>-2.724704099565095</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.27824930974537</v>
+        <v>-1.303589339227386</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1.790182768703062</v>
+        <v>1.7361490673077</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.707297715414214</v>
+        <v>-3.284181483752306</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.946885969808612</v>
+        <v>-2.485876976635552</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-0.917910208571783</v>
+        <v>-0.4963532603917287</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.60002316524055</v>
+        <v>-3.132116645754536</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.201290943226432</v>
+        <v>-2.944922915091553</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-1.097770935247034</v>
+        <v>-1.024513825467338</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.6497128658257054</v>
+        <v>0.7490601911202788</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>2.176613439167241</v>
+        <v>2.276521475185916</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>2.465085323877169</v>
+        <v>2.334688212550809</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.610151861868104</v>
+        <v>1.506629853086551</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.7728081400792775</v>
+        <v>-0.8417278823006811</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; 0.6376</t>
+          <t>X &lt; 0.6373</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.152648553330707</v>
+        <v>-4.328293643068804</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-1.204564129677209</v>
+        <v>-1.366016182770117</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.5283240600358425</v>
+        <v>0.3614579501273028</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.442014218423395</v>
+        <v>-3.14502164502165</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.455913527616651</v>
+        <v>-2.119119270822061</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-1.85366144920107</v>
+        <v>-1.846333752003133</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.853005954808708</v>
+        <v>-2.513050447289189</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.539586793717397</v>
+        <v>-4.340216909431767</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.856666511215778</v>
+        <v>-2.088287450216569</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.572438966082224</v>
+        <v>-0.4730916407876506</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>2.271640363462453</v>
+        <v>2.371548399481128</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>1.567598287578797</v>
+        <v>1.515080990504558</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2300162416048437</v>
+        <v>0.2052889175992689</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.1558689032756604</v>
+        <v>-0.7651784155073074</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; 0.6816</t>
+          <t>X &lt; 0.6812</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.424312256949449</v>
+        <v>-3.329783956034525</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.08266816133402699</v>
+        <v>-0.1026785814043407</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1.881051019948664</v>
+        <v>1.851001270656546</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.9287523836773914</v>
+        <v>-0.8360160965794847</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.629535074258655</v>
+        <v>-0.6210398854187176</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.1417726046655332</v>
+        <v>0.1212292014753231</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.127771877823392</v>
+        <v>-1.113135807937937</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.120906872321022</v>
+        <v>-1.217742387708185</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.7138455683125926</v>
+        <v>0.5233094204691113</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>1.048760895205483</v>
+        <v>0.878726122673001</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.739794334101695</v>
+        <v>2.561378127967096</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>1.964207496757474</v>
+        <v>1.676148638916899</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1188784961756539</v>
+        <v>-0.1341036272695746</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.605504618443419</v>
+        <v>-1.064304048273065</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; 0.7256</t>
+          <t>X &lt; 0.7252</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.943281621932201</v>
+        <v>-1.883993756908453</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.02976167568497345</v>
+        <v>0.0285748892403177</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.427104986270429</v>
+        <v>1.426951596266107</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.6762174850521134</v>
+        <v>-0.5937019969278126</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.7582472703785399</v>
+        <v>-0.5453167292775802</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.07869510458029083</v>
+        <v>0.2651031981434997</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.1858713697937873</v>
+        <v>0.0252356393839932</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.6529400135805261</v>
+        <v>-0.5219983809492845</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1.624207326299569</v>
+        <v>1.697464436079265</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.673569105509273</v>
+        <v>1.772916430803846</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.188292407680741</v>
+        <v>2.288200443699417</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.246910627441601</v>
+        <v>1.267230490416829</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1060390534074713</v>
+        <v>0.1526481034213489</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1515945234538236</v>
+        <v>0.04198073522088919</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; 0.7695</t>
+          <t>X &lt; 0.7691</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.223660945887282</v>
+        <v>0.3984754327307485</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.386399956845644</v>
+        <v>1.523909425602099</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.407717337693931</v>
+        <v>1.268867692488506</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.6066483647648582</v>
+        <v>-0.6816920943134619</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.374771019390451</v>
+        <v>-0.4774599592598321</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.494643164998763</v>
+        <v>-0.6207632060442307</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.1160567678073932</v>
+        <v>0.01206198073585796</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.7616445913363634</v>
+        <v>0.5943491155597869</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>1.95240096054377</v>
+        <v>1.747493953494541</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.936974514700708</v>
+        <v>1.758157723166342</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>2.370152490645012</v>
+        <v>2.110345509288116</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.788958951916698</v>
+        <v>1.612184012995144</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.647748126497291</v>
+        <v>1.356108144845791</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.9772525837487507</v>
+        <v>0.4924965395454421</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; 0.8135</t>
+          <t>X &lt; 0.8131</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.09419126560297997</v>
+        <v>0.1665477040209353</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.272704743354609</v>
+        <v>1.319358464019324</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.092525633277681</v>
+        <v>1.032801611824674</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.3287214045070712</v>
+        <v>-0.3378502526412461</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2712820038820567</v>
+        <v>-0.2911937129929569</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1889617376878334</v>
+        <v>-0.1255893302940763</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4790160750890138</v>
+        <v>0.4568413972007264</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.1194743130227067</v>
+        <v>0.05011926339002315</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1.671395382306379</v>
+        <v>1.576143662408192</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>1.036530349417376</v>
+        <v>0.9671378528069638</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>1.8620732968553</v>
+        <v>1.729699875732742</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.097019356860677</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.000144365616229</v>
+        <v>0.9630631441063002</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.4250718843098227</v>
+        <v>0.2454055356598062</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; 0.8574</t>
+          <t>X &lt; 0.857</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>1195</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.1418982908644821</v>
+        <v>0.2444791600879768</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.8621027057107256</v>
+        <v>1.044555701485983</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.9669150012221337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.1066483647648582</v>
+        <v>-0.05472013366750872</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.5996918794952464</v>
+        <v>-0.4604270858140751</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.1980991643183216</v>
+        <v>0.3136115658369292</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.363597312141394</v>
+        <v>0.5035820430275066</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1034713316453448</v>
+        <v>-0.08337292085790438</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.086589047278082</v>
+        <v>1.180923693777707</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.48687875803747</v>
+        <v>0.5244591296991246</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.080630957542027</v>
+        <v>1.157138765845048</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.4945793487945309</v>
+        <v>0.4621674278961336</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.4563057080219508</v>
+        <v>0.4017375348051146</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3951016288856195</v>
+        <v>0.2323723549794678</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.9014</t>
+          <t>X &lt; 0.901</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1496</v>
+        <v>1501</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.9173764430426701</v>
+        <v>-0.9143671440359213</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3994873531391008</v>
+        <v>-0.4006741395837565</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.07067805518636305</v>
+        <v>0.1370582646497809</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.295396700317454</v>
+        <v>-0.1987928904096634</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.5311804228572257</v>
+        <v>-0.4219076334906617</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.06910277844119861</v>
+        <v>0.1170122831992018</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.6510590858417018</v>
+        <v>0.7216921886510477</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.7839904420549644</v>
+        <v>0.8253374274402461</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.856341618865514</v>
+        <v>0.8922458527846828</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.339756155868983</v>
+        <v>0.4015285311302534</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.2393912217582326</v>
+        <v>0.2640103354262706</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.244733550498168</v>
+        <v>0.2555548209590555</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.6639115551677506</v>
+        <v>0.65986391638058</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.59373452441735</v>
+        <v>0.5091752674032719</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.9453</t>
+          <t>X &lt; 0.9449</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1820</v>
+        <v>1825</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.194654399445142</v>
+        <v>-1.170582027183322</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.8901316802484232</v>
+        <v>-0.9204223892550942</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.02600870266083177</v>
+        <v>-0.02616209266515312</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5231324830562087</v>
+        <v>-0.5530925013683685</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.5387735342989046</v>
+        <v>-0.5497308048818681</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.1721729538798016</v>
+        <v>0.1061964763891723</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.471234524438195</v>
+        <v>0.428682149615824</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.3879378104760178</v>
+        <v>0.376355930699134</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.4366047767602623</v>
+        <v>0.3697813770470404</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.02954208974503558</v>
+        <v>-0.07048555993232242</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.1486531757318517</v>
+        <v>-0.2198314869204694</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.3030147095309346</v>
+        <v>-0.3808428317473656</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.08838931235533209</v>
+        <v>-0.17326103228379</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2711358992766009</v>
+        <v>-0.4173668551999299</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.9893</t>
+          <t>X &lt; 0.9889</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2171</v>
+        <v>2178</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8517283297541738</v>
+        <v>-0.8602493134296054</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.5354247486555508</v>
+        <v>-0.5398730457603946</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.3794847979355964</v>
+        <v>-0.4044580910180926</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.9590358762432771</v>
+        <v>-0.962647444298824</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.6459714502445664</v>
+        <v>-0.6262085118562553</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.09388741763722663</v>
+        <v>-0.1240651948721876</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.270509541609286</v>
+        <v>-0.2764644033636969</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.09419583245484375</v>
+        <v>-0.1207470039649721</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.3758818487505806</v>
+        <v>0.3266602529794653</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.290128901602273</v>
+        <v>-0.3135135987262458</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.2391860327499842</v>
+        <v>-0.2880856348757419</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3170831868973565</v>
+        <v>-0.3676599443428046</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.07119758210190952</v>
+        <v>0.01771472780778538</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1836186261305812</v>
+        <v>-0.2842045975046688</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.8409160305343519</v>
+        <v>-0.9101118248869824</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8921021235981783</v>
+        <v>-0.9120164010392386</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.5268735083532263</v>
+        <v>-0.5238563619284022</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.415071734112594</v>
+        <v>-0.393972320713722</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2912549715034629</v>
+        <v>-0.3227731029786938</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.3724938041245451</v>
+        <v>-0.3702437891237267</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.3771080480523068</v>
+        <v>-0.3691444267311965</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2034077691318004</v>
+        <v>-0.2523389186282472</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2383929009168</v>
+        <v>0.1735533044635176</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.1708207672079354</v>
+        <v>-0.2093935128244055</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.3531213550966115</v>
+        <v>-0.4135339603604962</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.4567095926180755</v>
+        <v>-0.5156878642781706</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.02798265766153918</v>
+        <v>0.01099789653274996</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.4458488267985175</v>
+        <v>-0.5014802875440623</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2790</v>
+        <v>2796</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.7296651370390066</v>
+        <v>-0.7613609326671451</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.340136433819765</v>
+        <v>-1.362121469842904</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.9843717213625141</v>
+        <v>-0.9870268983575414</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.7992654545038604</v>
+        <v>-0.7857142857142918</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.5315616660722853</v>
+        <v>-0.4892491409519195</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.4294064642540931</v>
+        <v>-0.4471327386542043</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.6572295247724966</v>
+        <v>-0.6671431975220443</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.8022945907417025</v>
+        <v>-0.8276605773651724</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.2711697149450316</v>
+        <v>-0.30874175776394</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6558057625275708</v>
+        <v>-0.6676204101096843</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.8048662340417607</v>
+        <v>-0.8359954785327588</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.929707251182009</v>
+        <v>-0.956655636732954</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5059667180393674</v>
+        <v>-0.5292098436973518</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.5826881463127194</v>
+        <v>-0.6378187728121745</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3022</v>
+        <v>3027</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.5508599434343893</v>
+        <v>-0.5325244814459822</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.040304037158066</v>
+        <v>-1.010532563191539</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.757500571059488</v>
+        <v>-0.7271324392546461</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6755654991326381</v>
+        <v>-0.663211458725975</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2383989482436419</v>
+        <v>-0.1959962197306666</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1872566533394391</v>
+        <v>-0.2351043347690904</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.5692910958563502</v>
+        <v>-0.6078599282372892</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.7059996471422636</v>
+        <v>-0.7587285411659437</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.1871921991560725</v>
+        <v>-0.249353274877457</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.6075009492202312</v>
+        <v>-0.6438555677135795</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.6946970685069047</v>
+        <v>-0.7489207180237827</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.7080800775491127</v>
+        <v>-0.7568041788094817</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.5805886924329826</v>
+        <v>-0.623560520168553</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.667205746041347</v>
+        <v>-0.7194517441672517</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3220</v>
+        <v>3228</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.4066126249616033</v>
+        <v>-0.4235585018576202</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.150925653009942</v>
+        <v>-1.155750258218468</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8479760168697936</v>
+        <v>-0.8526315998731562</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7630919831043883</v>
+        <v>-0.7536785824753736</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4790717883284756</v>
+        <v>-0.4387211041881898</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.2888224127139978</v>
+        <v>-0.2728639050184327</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.3877006040807842</v>
+        <v>-0.3786141624350776</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.513683976549693</v>
+        <v>-0.5180519852314021</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.0005930663427733407</v>
+        <v>-0.01164210959159817</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.6011867721707134</v>
+        <v>-0.5877159675821844</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.6335456849850658</v>
+        <v>-0.6370097133530166</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.5508648016187436</v>
+        <v>-0.547873635635078</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4569890476523</v>
+        <v>-0.4784914569031429</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.6175286369736881</v>
+        <v>-0.6457961807927717</v>
       </c>
     </row>
     <row r="22">
@@ -4740,49 +4740,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3384</v>
+        <v>3393</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.5527441141375249</v>
+        <v>-0.5254014455867804</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.176907777308429</v>
+        <v>-1.152112439454598</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.9669913286772243</v>
+        <v>-0.9418665570807008</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7031421773753479</v>
+        <v>-0.6943008447862908</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.6066974227234994</v>
+        <v>-0.5657212125696276</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.2933186052065935</v>
+        <v>-0.3063904698585418</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.4209943890428036</v>
+        <v>-0.4099469959372826</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4590774045527084</v>
+        <v>-0.5064557529129274</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.09082076925290039</v>
+        <v>-0.1444317082718172</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.5407633246504844</v>
+        <v>-0.5853442360676553</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.6995478958071999</v>
+        <v>-0.7305745216008006</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5896926622036318</v>
+        <v>-0.6134976222329627</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.4616482794201886</v>
+        <v>-0.4619574425484743</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.5739182233355251</v>
+        <v>-0.5795379649383463</v>
       </c>
     </row>
     <row r="23">
@@ -4792,517 +4792,517 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3522</v>
+        <v>3532</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2885539371821579</v>
+        <v>-0.2649833301114981</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.6965163850582812</v>
+        <v>-0.6752098139976326</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.8780424865587051</v>
+        <v>-0.8560576980184678</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.7892644463050615</v>
+        <v>-0.754430226456229</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6043686740202858</v>
+        <v>-0.550179448631809</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4615865511149764</v>
+        <v>-0.4599508389026568</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.5876298723145297</v>
+        <v>-0.5901449214424943</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.52916148538268</v>
+        <v>-0.5597841549101119</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.1777194339650308</v>
+        <v>-0.2134686171385951</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.5866193404441091</v>
+        <v>-0.6128489806360946</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.690476917284812</v>
+        <v>-0.7038032368875236</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.4984442620676646</v>
+        <v>-0.5041537604168056</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.5053870192732219</v>
+        <v>-0.5156143429476217</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.5760325925889589</v>
+        <v>-0.590469137270702</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 1.297</t>
+          <t>X &lt; 1.296</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3635</v>
+        <v>3644</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.09604760948172242</v>
+        <v>-0.08744552321712007</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6509175883637397</v>
+        <v>-0.6431246165050553</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.7567583136192653</v>
+        <v>-0.7209354165717272</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.7489666089349498</v>
+        <v>-0.7006104002817253</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.5590432965652781</v>
+        <v>-0.5176248748071117</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4938032513876962</v>
+        <v>-0.4765935990346932</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.700945307348853</v>
+        <v>-0.6868941474486832</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5764233636760707</v>
+        <v>-0.5895387070036548</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4026327401088352</v>
+        <v>-0.4195693093873345</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.6329286476484555</v>
+        <v>-0.6399969028188863</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.7674188891421636</v>
+        <v>-0.7618553975299633</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5528104574045827</v>
+        <v>-0.5391247545150435</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.5451071422931761</v>
+        <v>-0.53494996627105</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.5515295084184899</v>
+        <v>-0.5449701212180003</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 1.341</t>
+          <t>X &lt; 1.34</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3723</v>
+        <v>3734</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.0451558592281387</v>
+        <v>-0.02613746591261901</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5445786965566839</v>
+        <v>-0.5266311488886828</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7643239636290673</v>
+        <v>-0.7457120934403818</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.5929194603983987</v>
+        <v>-0.5747317371214749</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4201254848487679</v>
+        <v>-0.3811513563835476</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4029779863224974</v>
+        <v>-0.4147404723221229</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.5803975718884118</v>
+        <v>-0.5946692030652443</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.469804140943161</v>
+        <v>-0.5108526208300717</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.3551748332088778</v>
+        <v>-0.3993805718544294</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.5732569914344694</v>
+        <v>-0.6075774610205968</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.628874148929043</v>
+        <v>-0.6511183368222078</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.4453319507070148</v>
+        <v>-0.4591186230119106</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.4208573381505758</v>
+        <v>-0.4377711274590084</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.4217588460317003</v>
+        <v>-0.4415210546701829</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 1.385</t>
+          <t>X &lt; 1.384</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3818</v>
+        <v>3829</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2491227650684209</v>
+        <v>-0.2444868248869767</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3845303220316012</v>
+        <v>-0.3813847683392666</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.6085763028165232</v>
+        <v>-0.5787413329588915</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.5426462749007044</v>
+        <v>-0.5390558099705913</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5181414715579606</v>
+        <v>-0.4928987759884151</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5463354512155334</v>
+        <v>-0.5449232980502927</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6430585612171242</v>
+        <v>-0.6436522398628171</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4683805481821466</v>
+        <v>-0.495347089907348</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4627446135871764</v>
+        <v>-0.4919739923012045</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.6703955971399083</v>
+        <v>-0.7011732089956695</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.6774024742572067</v>
+        <v>-0.6964908948507329</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.5761165882557719</v>
+        <v>-0.5861184670655746</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.5103668261563072</v>
+        <v>-0.5229158840309935</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4008856675805887</v>
+        <v>-0.415950125627127</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 1.429</t>
+          <t>X &lt; 1.428</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3871</v>
+        <v>3880</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1379706134385756</v>
+        <v>-0.1071305861308787</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.3707526515404922</v>
+        <v>-0.3914894241816569</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.6486457906819183</v>
+        <v>-0.6171374666270211</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.5045483905314114</v>
+        <v>-0.4733980011757879</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.5650410106440589</v>
+        <v>-0.511429301928068</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.5372390622393795</v>
+        <v>-0.5334623722249034</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.633795650276582</v>
+        <v>-0.6316885659273126</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.4936812972623841</v>
+        <v>-0.5429377593686908</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.3599638506907326</v>
+        <v>-0.3855871242177003</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.5247599731632704</v>
+        <v>-0.5513138295010478</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.5602470158140207</v>
+        <v>-0.6008947716275443</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4340267002811657</v>
+        <v>-0.4654482815578689</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.4523705959112689</v>
+        <v>-0.4855375603640368</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3154496325595986</v>
+        <v>-0.3509214378859866</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 1.473</t>
+          <t>X &lt; 1.472</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3916</v>
+        <v>3927</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.1011756385771108</v>
+        <v>-0.0856386083345555</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4261143435574439</v>
+        <v>-0.4112167922165284</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.679896171964117</v>
+        <v>-0.6643192529422492</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5359657361352106</v>
+        <v>-0.5207607433217234</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.6274219942936767</v>
+        <v>-0.6151340565445906</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.5965445202336213</v>
+        <v>-0.582757470633247</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.6929803397679564</v>
+        <v>-0.6805376765613218</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.5088533451284434</v>
+        <v>-0.5222723380403096</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.4283816660107931</v>
+        <v>-0.4436057146686139</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.5500397624983577</v>
+        <v>-0.5664944832130203</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.5619595469178691</v>
+        <v>-0.5783736932750472</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.4367945172130092</v>
+        <v>-0.4438516492163416</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.4597552320702505</v>
+        <v>-0.4684232675877595</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3218155566978282</v>
+        <v>-0.3324332553589997</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 1.517</t>
+          <t>X &lt; 1.516</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3946</v>
+        <v>3957</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.1444674324035162</v>
+        <v>-0.1291594439345971</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4539010119256233</v>
+        <v>-0.4390550390751002</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.6834871045119257</v>
+        <v>-0.6680200922067954</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5143834507102554</v>
+        <v>-0.4993516317268174</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5839391820830571</v>
+        <v>-0.5714865756483718</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.5510287339513127</v>
+        <v>-0.5372795367935126</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6473640527028692</v>
+        <v>-0.6347672366819879</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.46816880220954</v>
+        <v>-0.4812159750229767</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.464691031096514</v>
+        <v>-0.4791532700083252</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.5412565023588556</v>
+        <v>-0.5568561147960338</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.5293157291574673</v>
+        <v>-0.5449308789767215</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.4301615815455051</v>
+        <v>-0.4362463340846787</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.4308038447224831</v>
+        <v>-0.4383596361171911</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3175314702540319</v>
+        <v>-0.3267765712917523</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 1.561</t>
+          <t>X &lt; 1.56</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3984</v>
+        <v>3995</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.06660529748456412</v>
+        <v>-0.05191367165513583</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3383483698444252</v>
+        <v>-0.3239429290143789</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.5694767624208126</v>
+        <v>-0.5544426286946234</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.4007144639135873</v>
+        <v>-0.3861138861138969</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.399571025799446</v>
+        <v>-0.387236364819735</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.4141971547585328</v>
+        <v>-0.40069293604747</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.4853311254670771</v>
+        <v>-0.4728029334100867</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.3122501594488014</v>
+        <v>-0.3250953288846574</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.2842784195735248</v>
+        <v>-0.2983582606021002</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.3681676154449463</v>
+        <v>-0.3831076243892113</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.2830036931361235</v>
+        <v>-0.298136791241177</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2094930918823366</v>
+        <v>-0.2149512898032313</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2642685189076275</v>
+        <v>-0.2707969243402317</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2000824547291771</v>
+        <v>-0.2079269731555939</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 1.605</t>
+          <t>X &lt; 1.604</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4016</v>
+        <v>4027</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1850609796532368</v>
+        <v>-0.1704237832925273</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.2936910014531975</v>
+        <v>-0.2795197173731978</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.4764439081545575</v>
+        <v>-0.4617606115108686</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.3079648078845736</v>
+        <v>-0.2937137193827084</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.3607764271773206</v>
+        <v>-0.3482507341542558</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.323210011485898</v>
+        <v>-0.3098484227562679</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.2950010682721498</v>
+        <v>-0.2826632627735677</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.151829216489709</v>
+        <v>-0.1645794558687825</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.09965605998716853</v>
+        <v>-0.1135005850073156</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.2144726998524007</v>
+        <v>-0.2288865932781192</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.1813421161010851</v>
+        <v>-0.1958138340816333</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.08322986646196284</v>
+        <v>-0.088006987508507</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.1159902948354699</v>
+        <v>-0.1216905190272755</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.100280857903627</v>
+        <v>-0.1069688907748585</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 1.649</t>
+          <t>X &lt; 1.648</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.07529056791406674</v>
+        <v>-0.06118246234698432</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.1927931403800187</v>
+        <v>-0.1789609927607145</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.3767772358279231</v>
+        <v>-0.3624270461044006</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1838088585920161</v>
+        <v>-0.1945812807881779</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.2641648874826856</v>
+        <v>-0.2516642326353065</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.2497378012689495</v>
+        <v>-0.2364946015035514</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.222180350778018</v>
+        <v>-0.2098110033053615</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.08261031589528045</v>
+        <v>-0.07050953006808669</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.08053518377148094</v>
+        <v>-0.0692504287736142</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.125525743240793</v>
+        <v>-0.1394855666904036</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.1432531893810562</v>
+        <v>-0.1324684985709013</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.0455099475123788</v>
+        <v>-0.06047338794149226</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.0558154514314424</v>
+        <v>-0.07151717062946261</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.03884343926137035</v>
+        <v>-0.0554524293585601</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4057</v>
+        <v>4068</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.0239135735318996</v>
+        <v>-0.02297631888355056</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.123067962870735</v>
+        <v>-0.1227006747487209</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.3079157895724904</v>
+        <v>-0.3070808331454842</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.1643690433977625</v>
+        <v>-0.1639108806838152</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2220407215988729</v>
+        <v>-0.222894328239498</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.206419976786357</v>
+        <v>-0.2065799827105934</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1793214915861228</v>
+        <v>-0.1802748384399635</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.09150385608270994</v>
+        <v>-0.09273155863428428</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.1143132309621535</v>
+        <v>-0.1161987997941054</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.1380571905973937</v>
+        <v>-0.1406607624513612</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1073095344109092</v>
+        <v>-0.1100136305827917</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.03445943441626298</v>
+        <v>-0.03807416021156484</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.04647916219601456</v>
+        <v>-0.05081164045718367</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.003981313660098351</v>
+        <v>-0.009128819613124506</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.03353472852749206</v>
+        <v>-0.03268932061556029</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.04069453485889341</v>
+        <v>-0.0405545350428369</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2998020098223719</v>
+        <v>-0.2989927103233541</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.1563054796313779</v>
+        <v>-0.1558727057017251</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.2403568301584471</v>
+        <v>-0.2409681036408386</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.2236359293918397</v>
+        <v>-0.2236553551311857</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1724703259230083</v>
+        <v>-0.1732505909897029</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.1113433815946294</v>
+        <v>-0.1123202677599551</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.1588292165113074</v>
+        <v>-0.1603010023403542</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.185826380309571</v>
+        <v>-0.1879023896779231</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.1314808218220165</v>
+        <v>-0.1337181506152447</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.08332758623219405</v>
+        <v>-0.08631222607077405</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.09696218052160077</v>
+        <v>-0.1005593673217575</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.05375691194916499</v>
+        <v>-0.05807633958939817</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.09183753224083802</v>
+        <v>-0.09095305999517933</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.08088534720218377</v>
+        <v>-0.08064299564595245</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.2673613132312624</v>
+        <v>-0.2666425636457959</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1239086721569009</v>
+        <v>-0.1235662148070915</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.2097256191782648</v>
+        <v>-0.210227481180695</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.1919012082157039</v>
+        <v>-0.1919122241638718</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.1168445599916339</v>
+        <v>-0.1175837274981504</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.05776779970327794</v>
+        <v>-0.05869250375071289</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.0808673047625561</v>
+        <v>-0.08225673217491902</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1354942716902485</v>
+        <v>-0.1373097741970568</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.08214930346647265</v>
+        <v>-0.08412056374030641</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.05848178525954495</v>
+        <v>-0.06103892720364001</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.04925071068424813</v>
+        <v>-0.05238172787089468</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.0542312583073965</v>
+        <v>-0.05786134233657236</v>
       </c>
     </row>
   </sheetData>
